--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113231562</v>
+        <v>113231514</v>
       </c>
       <c r="B9" t="n">
-        <v>90047</v>
+        <v>78105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546830</v>
+        <v>546602</v>
       </c>
       <c r="R9" t="n">
-        <v>7205715</v>
+        <v>7205952</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113231551</v>
+        <v>113231531</v>
       </c>
       <c r="B10" t="n">
-        <v>56765</v>
+        <v>79169</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,39 +1592,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546819</v>
+        <v>546605</v>
       </c>
       <c r="R10" t="n">
-        <v>7205844</v>
+        <v>7206002</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113231514</v>
+        <v>113231562</v>
       </c>
       <c r="B11" t="n">
-        <v>78105</v>
+        <v>90047</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546602</v>
+        <v>546830</v>
       </c>
       <c r="R11" t="n">
-        <v>7205952</v>
+        <v>7205715</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113231531</v>
+        <v>113231551</v>
       </c>
       <c r="B12" t="n">
-        <v>79169</v>
+        <v>56765</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,34 +1816,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546605</v>
+        <v>546819</v>
       </c>
       <c r="R12" t="n">
-        <v>7206002</v>
+        <v>7205844</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3713,10 +3713,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113231550</v>
+        <v>113231549</v>
       </c>
       <c r="B29" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3729,31 +3729,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546818</v>
+        <v>546817</v>
       </c>
       <c r="R29" t="n">
         <v>7205855</v>
@@ -3825,10 +3830,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113231549</v>
+        <v>113231554</v>
       </c>
       <c r="B30" t="n">
-        <v>56765</v>
+        <v>78105</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3841,39 +3846,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546817</v>
+        <v>546814</v>
       </c>
       <c r="R30" t="n">
-        <v>7205855</v>
+        <v>7205823</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3942,7 +3942,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113231554</v>
+        <v>113231550</v>
       </c>
       <c r="B31" t="n">
         <v>78105</v>
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546814</v>
+        <v>546818</v>
       </c>
       <c r="R31" t="n">
-        <v>7205823</v>
+        <v>7205855</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113231536</v>
+        <v>113231538</v>
       </c>
       <c r="B2" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546624</v>
+        <v>546640</v>
       </c>
       <c r="R2" t="n">
-        <v>7205956</v>
+        <v>7205922</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113231517</v>
+        <v>113231524</v>
       </c>
       <c r="B3" t="n">
-        <v>74286</v>
+        <v>78121</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546435</v>
+        <v>546496</v>
       </c>
       <c r="R3" t="n">
-        <v>7205979</v>
+        <v>7205951</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113231553</v>
+        <v>113231517</v>
       </c>
       <c r="B4" t="n">
-        <v>56765</v>
+        <v>74302</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546814</v>
+        <v>546435</v>
       </c>
       <c r="R4" t="n">
-        <v>7205823</v>
+        <v>7205979</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113231521</v>
+        <v>113231552</v>
       </c>
       <c r="B5" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546488</v>
+        <v>546819</v>
       </c>
       <c r="R5" t="n">
-        <v>7205982</v>
+        <v>7205843</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113231534</v>
+        <v>113231533</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546624</v>
+        <v>546607</v>
       </c>
       <c r="R6" t="n">
-        <v>7205957</v>
+        <v>7206002</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113231532</v>
+        <v>113231548</v>
       </c>
       <c r="B7" t="n">
-        <v>79202</v>
+        <v>78121</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546604</v>
+        <v>546793</v>
       </c>
       <c r="R7" t="n">
-        <v>7206002</v>
+        <v>7205849</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113231555</v>
+        <v>113231514</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546821</v>
+        <v>546602</v>
       </c>
       <c r="R8" t="n">
-        <v>7205745</v>
+        <v>7205952</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113231514</v>
+        <v>113231515</v>
       </c>
       <c r="B9" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546602</v>
+        <v>546574</v>
       </c>
       <c r="R9" t="n">
-        <v>7205952</v>
+        <v>7205984</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113231531</v>
+        <v>113231539</v>
       </c>
       <c r="B10" t="n">
-        <v>79169</v>
+        <v>90387</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546605</v>
+        <v>546673</v>
       </c>
       <c r="R10" t="n">
-        <v>7206002</v>
+        <v>7205890</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113231562</v>
+        <v>113231560</v>
       </c>
       <c r="B11" t="n">
-        <v>90047</v>
+        <v>56910</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,34 +1699,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546830</v>
+        <v>546825</v>
       </c>
       <c r="R11" t="n">
-        <v>7205715</v>
+        <v>7205775</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113231551</v>
+        <v>113231528</v>
       </c>
       <c r="B12" t="n">
-        <v>56765</v>
+        <v>90727</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,43 +1811,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546819</v>
+        <v>546576</v>
       </c>
       <c r="R12" t="n">
-        <v>7205844</v>
+        <v>7206034</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113231539</v>
+        <v>113231555</v>
       </c>
       <c r="B13" t="n">
-        <v>90371</v>
+        <v>79185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1923,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546673</v>
+        <v>546821</v>
       </c>
       <c r="R13" t="n">
-        <v>7205890</v>
+        <v>7205745</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113231530</v>
+        <v>113231519</v>
       </c>
       <c r="B14" t="n">
-        <v>78105</v>
+        <v>90045</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546576</v>
+        <v>546487</v>
       </c>
       <c r="R14" t="n">
-        <v>7206032</v>
+        <v>7205984</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113231538</v>
+        <v>113231531</v>
       </c>
       <c r="B15" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,21 +2151,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546640</v>
+        <v>546605</v>
       </c>
       <c r="R15" t="n">
-        <v>7205922</v>
+        <v>7206002</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113231546</v>
+        <v>113231540</v>
       </c>
       <c r="B16" t="n">
-        <v>78105</v>
+        <v>90063</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,21 +2263,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546772</v>
+        <v>546672</v>
       </c>
       <c r="R16" t="n">
-        <v>7205856</v>
+        <v>7205887</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113231518</v>
+        <v>113231532</v>
       </c>
       <c r="B17" t="n">
-        <v>78105</v>
+        <v>79218</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,25 +2371,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546433</v>
+        <v>546604</v>
       </c>
       <c r="R17" t="n">
-        <v>7205978</v>
+        <v>7206002</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113231527</v>
+        <v>113231525</v>
       </c>
       <c r="B18" t="n">
-        <v>79168</v>
+        <v>79211</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2489,25 +2483,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546542</v>
+        <v>546543</v>
       </c>
       <c r="R18" t="n">
-        <v>7206042</v>
+        <v>7206040</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2589,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113231563</v>
+        <v>113231543</v>
       </c>
       <c r="B19" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,34 +2599,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546831</v>
+        <v>546727</v>
       </c>
       <c r="R19" t="n">
-        <v>7205718</v>
+        <v>7205919</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2673,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113231559</v>
+        <v>113231513</v>
       </c>
       <c r="B20" t="n">
-        <v>79202</v>
+        <v>79185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2713,25 +2712,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2740,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546819</v>
+        <v>546603</v>
       </c>
       <c r="R20" t="n">
-        <v>7205732</v>
+        <v>7205952</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2775,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2785,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113231785</v>
+        <v>113231542</v>
       </c>
       <c r="B21" t="n">
-        <v>57362</v>
+        <v>79185</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,42 +2824,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102125</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546816</v>
+        <v>546717</v>
       </c>
       <c r="R21" t="n">
-        <v>7205730</v>
+        <v>7205909</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2897,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113231540</v>
+        <v>113231512</v>
       </c>
       <c r="B22" t="n">
-        <v>90047</v>
+        <v>79185</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2945,21 +2940,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546672</v>
+        <v>546610</v>
       </c>
       <c r="R22" t="n">
-        <v>7205887</v>
+        <v>7205953</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3004,7 +2999,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +3009,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113231533</v>
+        <v>113231559</v>
       </c>
       <c r="B23" t="n">
-        <v>78105</v>
+        <v>79218</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,25 +3048,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3081,10 +3076,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546607</v>
+        <v>546819</v>
       </c>
       <c r="R23" t="n">
-        <v>7206002</v>
+        <v>7205732</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3116,7 +3111,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3126,7 +3121,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,10 +3148,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113231545</v>
+        <v>113231527</v>
       </c>
       <c r="B24" t="n">
-        <v>79169</v>
+        <v>79184</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,21 +3164,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +3188,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546772</v>
+        <v>546542</v>
       </c>
       <c r="R24" t="n">
-        <v>7205856</v>
+        <v>7206042</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3228,7 +3223,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3233,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113231537</v>
+        <v>113231562</v>
       </c>
       <c r="B25" t="n">
-        <v>79168</v>
+        <v>90063</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,21 +3276,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3305,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546642</v>
+        <v>546830</v>
       </c>
       <c r="R25" t="n">
-        <v>7205923</v>
+        <v>7205715</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3340,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3345,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113231547</v>
+        <v>113231518</v>
       </c>
       <c r="B26" t="n">
-        <v>74282</v>
+        <v>78121</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3393,21 +3388,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3417,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546793</v>
+        <v>546433</v>
       </c>
       <c r="R26" t="n">
-        <v>7205849</v>
+        <v>7205978</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3452,7 +3447,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3457,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,10 +3484,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113231528</v>
+        <v>113231521</v>
       </c>
       <c r="B27" t="n">
-        <v>90711</v>
+        <v>78121</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,25 +3496,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3529,10 +3524,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546576</v>
+        <v>546488</v>
       </c>
       <c r="R27" t="n">
-        <v>7206034</v>
+        <v>7205982</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3564,7 +3559,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,7 +3569,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,10 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113231541</v>
+        <v>113231530</v>
       </c>
       <c r="B28" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3641,10 +3636,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546672</v>
+        <v>546576</v>
       </c>
       <c r="R28" t="n">
-        <v>7205887</v>
+        <v>7206032</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3676,7 +3671,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3686,7 +3681,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3713,10 +3708,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113231549</v>
+        <v>113231561</v>
       </c>
       <c r="B29" t="n">
-        <v>56765</v>
+        <v>74302</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3729,39 +3724,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546817</v>
+        <v>546831</v>
       </c>
       <c r="R29" t="n">
-        <v>7205855</v>
+        <v>7205718</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3793,7 +3783,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3803,7 +3793,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3830,10 +3820,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113231554</v>
+        <v>113231551</v>
       </c>
       <c r="B30" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3846,34 +3836,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546814</v>
+        <v>546819</v>
       </c>
       <c r="R30" t="n">
-        <v>7205823</v>
+        <v>7205844</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3905,7 +3900,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3915,7 +3910,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3942,10 +3937,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113231550</v>
+        <v>113231537</v>
       </c>
       <c r="B31" t="n">
-        <v>78105</v>
+        <v>79184</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3958,21 +3953,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3982,10 +3977,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546818</v>
+        <v>546642</v>
       </c>
       <c r="R31" t="n">
-        <v>7205855</v>
+        <v>7205923</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4017,7 +4012,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4027,7 +4022,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4054,10 +4049,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113231515</v>
+        <v>113231549</v>
       </c>
       <c r="B32" t="n">
-        <v>79169</v>
+        <v>56765</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4070,34 +4065,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546574</v>
+        <v>546817</v>
       </c>
       <c r="R32" t="n">
-        <v>7205984</v>
+        <v>7205855</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4166,10 +4166,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113231535</v>
+        <v>113231547</v>
       </c>
       <c r="B33" t="n">
-        <v>90589</v>
+        <v>74298</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4178,25 +4178,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>760</v>
+        <v>310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546623</v>
+        <v>546793</v>
       </c>
       <c r="R33" t="n">
-        <v>7205959</v>
+        <v>7205849</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4278,10 +4278,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113231543</v>
+        <v>113231557</v>
       </c>
       <c r="B34" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4294,39 +4294,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546727</v>
+        <v>546821</v>
       </c>
       <c r="R34" t="n">
-        <v>7205919</v>
+        <v>7205743</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4358,7 +4353,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4368,7 +4363,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4395,10 +4390,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113231523</v>
+        <v>113231545</v>
       </c>
       <c r="B35" t="n">
-        <v>56910</v>
+        <v>79185</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4411,43 +4406,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546496</v>
+        <v>546772</v>
       </c>
       <c r="R35" t="n">
-        <v>7205950</v>
+        <v>7205856</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4479,7 +4465,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4489,7 +4475,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4516,10 +4502,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113231516</v>
+        <v>113231558</v>
       </c>
       <c r="B36" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4532,21 +4518,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4556,10 +4542,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546573</v>
+        <v>546816</v>
       </c>
       <c r="R36" t="n">
-        <v>7205984</v>
+        <v>7205730</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4591,7 +4577,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4601,7 +4587,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4628,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113231548</v>
+        <v>113231553</v>
       </c>
       <c r="B37" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4644,34 +4630,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546793</v>
+        <v>546814</v>
       </c>
       <c r="R37" t="n">
-        <v>7205849</v>
+        <v>7205823</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4703,7 +4694,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4713,7 +4704,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4740,10 +4731,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113231556</v>
+        <v>113231563</v>
       </c>
       <c r="B38" t="n">
-        <v>56872</v>
+        <v>78121</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4752,42 +4743,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546836</v>
+        <v>546831</v>
       </c>
       <c r="R38" t="n">
-        <v>7205771</v>
+        <v>7205718</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4819,7 +4806,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4829,7 +4816,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4856,10 +4843,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113231524</v>
+        <v>113231550</v>
       </c>
       <c r="B39" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4896,10 +4883,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546496</v>
+        <v>546818</v>
       </c>
       <c r="R39" t="n">
-        <v>7205951</v>
+        <v>7205855</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4931,7 +4918,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4941,7 +4928,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4968,10 +4955,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113231525</v>
+        <v>113231541</v>
       </c>
       <c r="B40" t="n">
-        <v>79195</v>
+        <v>78121</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4980,25 +4967,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5008,10 +4995,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546543</v>
+        <v>546672</v>
       </c>
       <c r="R40" t="n">
-        <v>7206040</v>
+        <v>7205887</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5043,7 +5030,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5053,7 +5040,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5080,10 +5067,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113231542</v>
+        <v>113231556</v>
       </c>
       <c r="B41" t="n">
-        <v>79169</v>
+        <v>56872</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5092,38 +5079,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546717</v>
+        <v>546836</v>
       </c>
       <c r="R41" t="n">
-        <v>7205909</v>
+        <v>7205771</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5155,7 +5146,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5165,7 +5156,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5192,10 +5183,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113231561</v>
+        <v>113231785</v>
       </c>
       <c r="B42" t="n">
-        <v>74286</v>
+        <v>57362</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5204,38 +5195,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>102125</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546831</v>
+        <v>546816</v>
       </c>
       <c r="R42" t="n">
-        <v>7205718</v>
+        <v>7205730</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5267,7 +5262,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5277,7 +5272,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5304,10 +5299,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113231512</v>
+        <v>113231536</v>
       </c>
       <c r="B43" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5320,21 +5315,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5344,10 +5339,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546610</v>
+        <v>546624</v>
       </c>
       <c r="R43" t="n">
-        <v>7205953</v>
+        <v>7205956</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5379,7 +5374,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5389,7 +5384,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5416,10 +5411,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113231519</v>
+        <v>113231516</v>
       </c>
       <c r="B44" t="n">
-        <v>90029</v>
+        <v>78121</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5432,21 +5427,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5456,7 +5451,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546487</v>
+        <v>546573</v>
       </c>
       <c r="R44" t="n">
         <v>7205984</v>
@@ -5491,7 +5486,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5501,7 +5496,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5528,10 +5523,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113231526</v>
+        <v>113231554</v>
       </c>
       <c r="B45" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5544,21 +5539,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5568,10 +5563,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546544</v>
+        <v>546814</v>
       </c>
       <c r="R45" t="n">
-        <v>7206041</v>
+        <v>7205823</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5603,7 +5598,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5613,7 +5608,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5640,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113231558</v>
+        <v>113231534</v>
       </c>
       <c r="B46" t="n">
-        <v>79169</v>
+        <v>79185</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5680,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546816</v>
+        <v>546624</v>
       </c>
       <c r="R46" t="n">
-        <v>7205730</v>
+        <v>7205957</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5715,7 +5710,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5725,7 +5720,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5752,10 +5747,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113231552</v>
+        <v>113231529</v>
       </c>
       <c r="B47" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5768,21 +5763,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5792,10 +5787,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546819</v>
+        <v>546577</v>
       </c>
       <c r="R47" t="n">
-        <v>7205843</v>
+        <v>7206034</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5827,7 +5822,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5837,7 +5832,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5864,10 +5859,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113231529</v>
+        <v>113231526</v>
       </c>
       <c r="B48" t="n">
-        <v>79169</v>
+        <v>79185</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5904,10 +5899,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546577</v>
+        <v>546544</v>
       </c>
       <c r="R48" t="n">
-        <v>7206034</v>
+        <v>7206041</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5939,7 +5934,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5949,7 +5944,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5976,10 +5971,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113231557</v>
+        <v>113231523</v>
       </c>
       <c r="B49" t="n">
-        <v>78105</v>
+        <v>56910</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5992,34 +5987,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546821</v>
+        <v>546496</v>
       </c>
       <c r="R49" t="n">
-        <v>7205743</v>
+        <v>7205950</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6051,7 +6055,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6061,7 +6065,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6088,10 +6092,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113231560</v>
+        <v>113231546</v>
       </c>
       <c r="B50" t="n">
-        <v>56910</v>
+        <v>78121</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6104,38 +6108,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546825</v>
+        <v>546772</v>
       </c>
       <c r="R50" t="n">
-        <v>7205775</v>
+        <v>7205856</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6204,10 +6204,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113231513</v>
+        <v>113231544</v>
       </c>
       <c r="B51" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6220,21 +6220,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546603</v>
+        <v>546727</v>
       </c>
       <c r="R51" t="n">
-        <v>7205952</v>
+        <v>7205919</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6316,10 +6316,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113231544</v>
+        <v>113231535</v>
       </c>
       <c r="B52" t="n">
-        <v>78105</v>
+        <v>90605</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6328,25 +6328,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546727</v>
+        <v>546623</v>
       </c>
       <c r="R52" t="n">
-        <v>7205919</v>
+        <v>7205959</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113231560</v>
+        <v>113231528</v>
       </c>
       <c r="B11" t="n">
-        <v>56910</v>
+        <v>90727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,42 +1695,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546825</v>
+        <v>546576</v>
       </c>
       <c r="R11" t="n">
-        <v>7205775</v>
+        <v>7206034</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113231528</v>
+        <v>113231560</v>
       </c>
       <c r="B12" t="n">
-        <v>90727</v>
+        <v>56910</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,38 +1807,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546576</v>
+        <v>546825</v>
       </c>
       <c r="R12" t="n">
-        <v>7206034</v>
+        <v>7205775</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113231519</v>
+        <v>113231531</v>
       </c>
       <c r="B14" t="n">
-        <v>90045</v>
+        <v>79185</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546487</v>
+        <v>546605</v>
       </c>
       <c r="R14" t="n">
-        <v>7205984</v>
+        <v>7206002</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113231531</v>
+        <v>113231543</v>
       </c>
       <c r="B15" t="n">
-        <v>79185</v>
+        <v>56765</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,34 +2151,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546605</v>
+        <v>546727</v>
       </c>
       <c r="R15" t="n">
-        <v>7206002</v>
+        <v>7205919</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2210,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113231540</v>
+        <v>113231532</v>
       </c>
       <c r="B16" t="n">
-        <v>90063</v>
+        <v>79218</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,25 +2264,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2287,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546672</v>
+        <v>546604</v>
       </c>
       <c r="R16" t="n">
-        <v>7205887</v>
+        <v>7206002</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2322,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113231532</v>
+        <v>113231525</v>
       </c>
       <c r="B17" t="n">
-        <v>79218</v>
+        <v>79211</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,21 +2380,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546604</v>
+        <v>546543</v>
       </c>
       <c r="R17" t="n">
-        <v>7206002</v>
+        <v>7206040</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113231525</v>
+        <v>113231519</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>90045</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,25 +2488,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546543</v>
+        <v>546487</v>
       </c>
       <c r="R18" t="n">
-        <v>7206040</v>
+        <v>7205984</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113231543</v>
+        <v>113231540</v>
       </c>
       <c r="B19" t="n">
-        <v>56765</v>
+        <v>90063</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,39 +2604,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546727</v>
+        <v>546672</v>
       </c>
       <c r="R19" t="n">
-        <v>7205919</v>
+        <v>7205887</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3148,10 +3148,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113231527</v>
+        <v>113231562</v>
       </c>
       <c r="B24" t="n">
-        <v>79184</v>
+        <v>90063</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3164,21 +3164,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546542</v>
+        <v>546830</v>
       </c>
       <c r="R24" t="n">
-        <v>7206042</v>
+        <v>7205715</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113231562</v>
+        <v>113231551</v>
       </c>
       <c r="B25" t="n">
-        <v>90063</v>
+        <v>56765</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3276,34 +3276,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546830</v>
+        <v>546819</v>
       </c>
       <c r="R25" t="n">
-        <v>7205715</v>
+        <v>7205844</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3335,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,7 +3350,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3820,10 +3825,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113231551</v>
+        <v>113231527</v>
       </c>
       <c r="B30" t="n">
-        <v>56765</v>
+        <v>79184</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3836,39 +3841,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546819</v>
+        <v>546542</v>
       </c>
       <c r="R30" t="n">
-        <v>7205844</v>
+        <v>7206042</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4278,10 +4278,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113231557</v>
+        <v>113231545</v>
       </c>
       <c r="B34" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4294,21 +4294,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546821</v>
+        <v>546772</v>
       </c>
       <c r="R34" t="n">
-        <v>7205743</v>
+        <v>7205856</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4390,7 +4390,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113231545</v>
+        <v>113231558</v>
       </c>
       <c r="B35" t="n">
         <v>79185</v>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546772</v>
+        <v>546816</v>
       </c>
       <c r="R35" t="n">
-        <v>7205856</v>
+        <v>7205730</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4502,10 +4502,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113231558</v>
+        <v>113231557</v>
       </c>
       <c r="B36" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4518,21 +4518,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546816</v>
+        <v>546821</v>
       </c>
       <c r="R36" t="n">
-        <v>7205730</v>
+        <v>7205743</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4731,10 +4731,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113231563</v>
+        <v>113231785</v>
       </c>
       <c r="B38" t="n">
-        <v>78121</v>
+        <v>57362</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4743,38 +4743,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546831</v>
+        <v>546816</v>
       </c>
       <c r="R38" t="n">
-        <v>7205718</v>
+        <v>7205730</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4806,7 +4810,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4816,7 +4820,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4843,7 +4847,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113231550</v>
+        <v>113231563</v>
       </c>
       <c r="B39" t="n">
         <v>78121</v>
@@ -4883,10 +4887,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546818</v>
+        <v>546831</v>
       </c>
       <c r="R39" t="n">
-        <v>7205855</v>
+        <v>7205718</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4918,7 +4922,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4928,7 +4932,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4955,7 +4959,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113231541</v>
+        <v>113231550</v>
       </c>
       <c r="B40" t="n">
         <v>78121</v>
@@ -4995,10 +4999,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546672</v>
+        <v>546818</v>
       </c>
       <c r="R40" t="n">
-        <v>7205887</v>
+        <v>7205855</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5030,7 +5034,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5040,7 +5044,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5067,10 +5071,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113231556</v>
+        <v>113231541</v>
       </c>
       <c r="B41" t="n">
-        <v>56872</v>
+        <v>78121</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5079,42 +5083,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546836</v>
+        <v>546672</v>
       </c>
       <c r="R41" t="n">
-        <v>7205771</v>
+        <v>7205887</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5183,10 +5183,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113231785</v>
+        <v>113231556</v>
       </c>
       <c r="B42" t="n">
-        <v>57362</v>
+        <v>56872</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5195,20 +5195,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102125</v>
+        <v>103031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546816</v>
+        <v>546836</v>
       </c>
       <c r="R42" t="n">
-        <v>7205730</v>
+        <v>7205771</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5299,10 +5299,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113231536</v>
+        <v>113231534</v>
       </c>
       <c r="B43" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5315,21 +5315,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
         <v>546624</v>
       </c>
       <c r="R43" t="n">
-        <v>7205956</v>
+        <v>7205957</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5411,10 +5411,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113231516</v>
+        <v>113231529</v>
       </c>
       <c r="B44" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546573</v>
+        <v>546577</v>
       </c>
       <c r="R44" t="n">
-        <v>7205984</v>
+        <v>7206034</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113231554</v>
+        <v>113231526</v>
       </c>
       <c r="B45" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5539,21 +5539,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546814</v>
+        <v>546544</v>
       </c>
       <c r="R45" t="n">
-        <v>7205823</v>
+        <v>7206041</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113231534</v>
+        <v>113231536</v>
       </c>
       <c r="B46" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5678,7 +5678,7 @@
         <v>546624</v>
       </c>
       <c r="R46" t="n">
-        <v>7205957</v>
+        <v>7205956</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5747,10 +5747,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113231529</v>
+        <v>113231516</v>
       </c>
       <c r="B47" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5763,21 +5763,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546577</v>
+        <v>546573</v>
       </c>
       <c r="R47" t="n">
-        <v>7206034</v>
+        <v>7205984</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5859,10 +5859,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113231526</v>
+        <v>113231554</v>
       </c>
       <c r="B48" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5875,21 +5875,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546544</v>
+        <v>546814</v>
       </c>
       <c r="R48" t="n">
-        <v>7206041</v>
+        <v>7205823</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113231538</v>
+        <v>113231534</v>
       </c>
       <c r="B2" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546640</v>
+        <v>546624</v>
       </c>
       <c r="R2" t="n">
-        <v>7205922</v>
+        <v>7205957</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113231524</v>
+        <v>113231548</v>
       </c>
       <c r="B3" t="n">
         <v>78121</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546496</v>
+        <v>546793</v>
       </c>
       <c r="R3" t="n">
-        <v>7205951</v>
+        <v>7205849</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113231552</v>
+        <v>113231545</v>
       </c>
       <c r="B5" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546819</v>
+        <v>546772</v>
       </c>
       <c r="R5" t="n">
-        <v>7205843</v>
+        <v>7205856</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113231533</v>
+        <v>113231559</v>
       </c>
       <c r="B6" t="n">
-        <v>78121</v>
+        <v>79218</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546607</v>
+        <v>546819</v>
       </c>
       <c r="R6" t="n">
-        <v>7206002</v>
+        <v>7205732</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113231548</v>
+        <v>113231551</v>
       </c>
       <c r="B7" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1251,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546793</v>
+        <v>546819</v>
       </c>
       <c r="R7" t="n">
-        <v>7205849</v>
+        <v>7205844</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113231514</v>
+        <v>113231529</v>
       </c>
       <c r="B8" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546602</v>
+        <v>546577</v>
       </c>
       <c r="R8" t="n">
-        <v>7205952</v>
+        <v>7206034</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113231515</v>
+        <v>113231530</v>
       </c>
       <c r="B9" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546574</v>
+        <v>546576</v>
       </c>
       <c r="R9" t="n">
-        <v>7205984</v>
+        <v>7206032</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113231539</v>
+        <v>113231513</v>
       </c>
       <c r="B10" t="n">
-        <v>90387</v>
+        <v>79185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1588,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546673</v>
+        <v>546603</v>
       </c>
       <c r="R10" t="n">
-        <v>7205890</v>
+        <v>7205952</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113231528</v>
+        <v>113231519</v>
       </c>
       <c r="B11" t="n">
-        <v>90727</v>
+        <v>90045</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1700,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546576</v>
+        <v>546487</v>
       </c>
       <c r="R11" t="n">
-        <v>7206034</v>
+        <v>7205984</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113231560</v>
+        <v>113231537</v>
       </c>
       <c r="B12" t="n">
-        <v>56910</v>
+        <v>79184</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,38 +1816,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546825</v>
+        <v>546642</v>
       </c>
       <c r="R12" t="n">
-        <v>7205775</v>
+        <v>7205923</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1874,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113231555</v>
+        <v>113231540</v>
       </c>
       <c r="B13" t="n">
-        <v>79185</v>
+        <v>90063</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546821</v>
+        <v>546672</v>
       </c>
       <c r="R13" t="n">
-        <v>7205745</v>
+        <v>7205887</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1986,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113231531</v>
+        <v>113231544</v>
       </c>
       <c r="B14" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,21 +2040,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546605</v>
+        <v>546727</v>
       </c>
       <c r="R14" t="n">
-        <v>7206002</v>
+        <v>7205919</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2098,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113231543</v>
+        <v>113231556</v>
       </c>
       <c r="B15" t="n">
-        <v>56765</v>
+        <v>56872</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,20 +2148,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2168,10 +2169,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546727</v>
+        <v>546836</v>
       </c>
       <c r="R15" t="n">
-        <v>7205919</v>
+        <v>7205771</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113231532</v>
+        <v>113231536</v>
       </c>
       <c r="B16" t="n">
-        <v>79218</v>
+        <v>78121</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,25 +2264,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546604</v>
+        <v>546624</v>
       </c>
       <c r="R16" t="n">
-        <v>7206002</v>
+        <v>7205956</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113231525</v>
+        <v>113231552</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>78121</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,25 +2376,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546543</v>
+        <v>546819</v>
       </c>
       <c r="R17" t="n">
-        <v>7206040</v>
+        <v>7205843</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113231519</v>
+        <v>113231561</v>
       </c>
       <c r="B18" t="n">
-        <v>90045</v>
+        <v>74302</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546487</v>
+        <v>546831</v>
       </c>
       <c r="R18" t="n">
-        <v>7205984</v>
+        <v>7205718</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113231540</v>
+        <v>113231527</v>
       </c>
       <c r="B19" t="n">
-        <v>90063</v>
+        <v>79184</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,21 +2604,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546672</v>
+        <v>546542</v>
       </c>
       <c r="R19" t="n">
-        <v>7205887</v>
+        <v>7206042</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113231513</v>
+        <v>113231549</v>
       </c>
       <c r="B20" t="n">
-        <v>79185</v>
+        <v>56765</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,34 +2716,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546603</v>
+        <v>546817</v>
       </c>
       <c r="R20" t="n">
-        <v>7205952</v>
+        <v>7205855</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2775,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2785,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,7 +2817,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113231542</v>
+        <v>113231555</v>
       </c>
       <c r="B21" t="n">
         <v>79185</v>
@@ -2852,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546717</v>
+        <v>546821</v>
       </c>
       <c r="R21" t="n">
-        <v>7205909</v>
+        <v>7205745</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2887,7 +2892,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2902,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113231512</v>
+        <v>113231539</v>
       </c>
       <c r="B22" t="n">
-        <v>79185</v>
+        <v>90387</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,25 +2941,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546610</v>
+        <v>546673</v>
       </c>
       <c r="R22" t="n">
-        <v>7205953</v>
+        <v>7205890</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,7 +3004,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +3014,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,10 +3041,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113231559</v>
+        <v>113231535</v>
       </c>
       <c r="B23" t="n">
-        <v>79218</v>
+        <v>90605</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3048,25 +3053,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>760</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3076,10 +3081,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546819</v>
+        <v>546623</v>
       </c>
       <c r="R23" t="n">
-        <v>7205732</v>
+        <v>7205959</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3111,7 +3116,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3121,7 +3126,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,10 +3153,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113231562</v>
+        <v>113231547</v>
       </c>
       <c r="B24" t="n">
-        <v>90063</v>
+        <v>74298</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3164,21 +3169,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3188,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546830</v>
+        <v>546793</v>
       </c>
       <c r="R24" t="n">
-        <v>7205715</v>
+        <v>7205849</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3223,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3233,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113231551</v>
+        <v>113231546</v>
       </c>
       <c r="B25" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3276,39 +3281,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546819</v>
+        <v>546772</v>
       </c>
       <c r="R25" t="n">
-        <v>7205844</v>
+        <v>7205856</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113231518</v>
+        <v>113231531</v>
       </c>
       <c r="B26" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3393,21 +3393,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546433</v>
+        <v>546605</v>
       </c>
       <c r="R26" t="n">
-        <v>7205978</v>
+        <v>7206002</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,10 +3489,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113231521</v>
+        <v>113231526</v>
       </c>
       <c r="B27" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3505,21 +3505,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546488</v>
+        <v>546544</v>
       </c>
       <c r="R27" t="n">
-        <v>7205982</v>
+        <v>7206041</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,7 +3601,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113231530</v>
+        <v>113231563</v>
       </c>
       <c r="B28" t="n">
         <v>78121</v>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546576</v>
+        <v>546831</v>
       </c>
       <c r="R28" t="n">
-        <v>7206032</v>
+        <v>7205718</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3713,10 +3713,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113231561</v>
+        <v>113231532</v>
       </c>
       <c r="B29" t="n">
-        <v>74302</v>
+        <v>79218</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3725,25 +3725,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546831</v>
+        <v>546604</v>
       </c>
       <c r="R29" t="n">
-        <v>7205718</v>
+        <v>7206002</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3825,10 +3825,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113231527</v>
+        <v>113231542</v>
       </c>
       <c r="B30" t="n">
-        <v>79184</v>
+        <v>79185</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3841,21 +3841,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546542</v>
+        <v>546717</v>
       </c>
       <c r="R30" t="n">
-        <v>7206042</v>
+        <v>7205909</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3937,10 +3937,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113231537</v>
+        <v>113231785</v>
       </c>
       <c r="B31" t="n">
-        <v>79184</v>
+        <v>57362</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3949,38 +3949,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>102125</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546642</v>
+        <v>546816</v>
       </c>
       <c r="R31" t="n">
-        <v>7205923</v>
+        <v>7205730</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4012,7 +4016,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4022,7 +4026,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4049,10 +4053,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113231549</v>
+        <v>113231521</v>
       </c>
       <c r="B32" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4065,39 +4069,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546817</v>
+        <v>546488</v>
       </c>
       <c r="R32" t="n">
-        <v>7205855</v>
+        <v>7205982</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4129,7 +4128,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4139,7 +4138,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4166,10 +4165,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113231547</v>
+        <v>113231538</v>
       </c>
       <c r="B33" t="n">
-        <v>74298</v>
+        <v>78121</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4182,21 +4181,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4206,10 +4205,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546793</v>
+        <v>546640</v>
       </c>
       <c r="R33" t="n">
-        <v>7205849</v>
+        <v>7205922</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4241,7 +4240,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4251,7 +4250,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4278,10 +4277,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113231545</v>
+        <v>113231533</v>
       </c>
       <c r="B34" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4294,21 +4293,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4318,10 +4317,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546772</v>
+        <v>546607</v>
       </c>
       <c r="R34" t="n">
-        <v>7205856</v>
+        <v>7206002</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4353,7 +4352,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4363,7 +4362,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4390,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113231558</v>
+        <v>113231525</v>
       </c>
       <c r="B35" t="n">
-        <v>79185</v>
+        <v>79211</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4402,25 +4401,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4430,10 +4429,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546816</v>
+        <v>546543</v>
       </c>
       <c r="R35" t="n">
-        <v>7205730</v>
+        <v>7206040</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4465,7 +4464,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4475,7 +4474,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4502,7 +4501,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113231557</v>
+        <v>113231550</v>
       </c>
       <c r="B36" t="n">
         <v>78121</v>
@@ -4542,10 +4541,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546821</v>
+        <v>546818</v>
       </c>
       <c r="R36" t="n">
-        <v>7205743</v>
+        <v>7205855</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4577,7 +4576,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4587,7 +4586,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4614,10 +4613,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113231553</v>
+        <v>113231558</v>
       </c>
       <c r="B37" t="n">
-        <v>56765</v>
+        <v>79185</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4630,39 +4629,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546814</v>
+        <v>546816</v>
       </c>
       <c r="R37" t="n">
-        <v>7205823</v>
+        <v>7205730</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4694,7 +4688,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4704,7 +4698,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4731,10 +4725,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113231785</v>
+        <v>113231528</v>
       </c>
       <c r="B38" t="n">
-        <v>57362</v>
+        <v>90727</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4743,42 +4737,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102125</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546816</v>
+        <v>546576</v>
       </c>
       <c r="R38" t="n">
-        <v>7205730</v>
+        <v>7206034</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4810,7 +4800,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4820,7 +4810,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4847,7 +4837,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113231563</v>
+        <v>113231514</v>
       </c>
       <c r="B39" t="n">
         <v>78121</v>
@@ -4887,10 +4877,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546831</v>
+        <v>546602</v>
       </c>
       <c r="R39" t="n">
-        <v>7205718</v>
+        <v>7205952</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4922,7 +4912,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4932,7 +4922,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4959,7 +4949,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113231550</v>
+        <v>113231524</v>
       </c>
       <c r="B40" t="n">
         <v>78121</v>
@@ -4999,10 +4989,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546818</v>
+        <v>546496</v>
       </c>
       <c r="R40" t="n">
-        <v>7205855</v>
+        <v>7205951</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5034,7 +5024,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5044,7 +5034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5071,10 +5061,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113231541</v>
+        <v>113231512</v>
       </c>
       <c r="B41" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5087,21 +5077,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5111,10 +5101,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546672</v>
+        <v>546610</v>
       </c>
       <c r="R41" t="n">
-        <v>7205887</v>
+        <v>7205953</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5146,7 +5136,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5156,7 +5146,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5183,10 +5173,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113231556</v>
+        <v>113231515</v>
       </c>
       <c r="B42" t="n">
-        <v>56872</v>
+        <v>79185</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5195,42 +5185,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546836</v>
+        <v>546574</v>
       </c>
       <c r="R42" t="n">
-        <v>7205771</v>
+        <v>7205984</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5262,7 +5248,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5272,7 +5258,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5299,10 +5285,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113231534</v>
+        <v>113231554</v>
       </c>
       <c r="B43" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5315,21 +5301,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5339,10 +5325,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546624</v>
+        <v>546814</v>
       </c>
       <c r="R43" t="n">
-        <v>7205957</v>
+        <v>7205823</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5374,7 +5360,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5384,7 +5370,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5411,10 +5397,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113231529</v>
+        <v>113231518</v>
       </c>
       <c r="B44" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5427,21 +5413,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5451,10 +5437,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546577</v>
+        <v>546433</v>
       </c>
       <c r="R44" t="n">
-        <v>7206034</v>
+        <v>7205978</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5486,7 +5472,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5496,7 +5482,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5523,10 +5509,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113231526</v>
+        <v>113231516</v>
       </c>
       <c r="B45" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5539,21 +5525,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5563,10 +5549,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546544</v>
+        <v>546573</v>
       </c>
       <c r="R45" t="n">
-        <v>7206041</v>
+        <v>7205984</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5598,7 +5584,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5608,7 +5594,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5635,10 +5621,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113231536</v>
+        <v>113231553</v>
       </c>
       <c r="B46" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5651,34 +5637,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546624</v>
+        <v>546814</v>
       </c>
       <c r="R46" t="n">
-        <v>7205956</v>
+        <v>7205823</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5710,7 +5701,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5720,7 +5711,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5747,7 +5738,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113231516</v>
+        <v>113231557</v>
       </c>
       <c r="B47" t="n">
         <v>78121</v>
@@ -5787,10 +5778,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546573</v>
+        <v>546821</v>
       </c>
       <c r="R47" t="n">
-        <v>7205984</v>
+        <v>7205743</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5822,7 +5813,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5832,7 +5823,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5859,10 +5850,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113231554</v>
+        <v>113231543</v>
       </c>
       <c r="B48" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5875,34 +5866,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546814</v>
+        <v>546727</v>
       </c>
       <c r="R48" t="n">
-        <v>7205823</v>
+        <v>7205919</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5934,7 +5930,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5944,7 +5940,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6092,10 +6088,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113231546</v>
+        <v>113231562</v>
       </c>
       <c r="B50" t="n">
-        <v>78121</v>
+        <v>90063</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6108,21 +6104,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6132,10 +6128,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546772</v>
+        <v>546830</v>
       </c>
       <c r="R50" t="n">
-        <v>7205856</v>
+        <v>7205715</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6167,7 +6163,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6177,7 +6173,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6204,7 +6200,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113231544</v>
+        <v>113231541</v>
       </c>
       <c r="B51" t="n">
         <v>78121</v>
@@ -6244,10 +6240,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546727</v>
+        <v>546672</v>
       </c>
       <c r="R51" t="n">
-        <v>7205919</v>
+        <v>7205887</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6279,7 +6275,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6289,7 +6285,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6316,10 +6312,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113231535</v>
+        <v>113231560</v>
       </c>
       <c r="B52" t="n">
-        <v>90605</v>
+        <v>56910</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6328,38 +6324,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>760</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546623</v>
+        <v>546825</v>
       </c>
       <c r="R52" t="n">
-        <v>7205959</v>
+        <v>7205775</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113231534</v>
+        <v>113231546</v>
       </c>
       <c r="B2" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546624</v>
+        <v>546772</v>
       </c>
       <c r="R2" t="n">
-        <v>7205957</v>
+        <v>7205856</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113231548</v>
+        <v>113231516</v>
       </c>
       <c r="B3" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546793</v>
+        <v>546573</v>
       </c>
       <c r="R3" t="n">
-        <v>7205849</v>
+        <v>7205984</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113231517</v>
+        <v>113231537</v>
       </c>
       <c r="B4" t="n">
-        <v>74302</v>
+        <v>79196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546435</v>
+        <v>546642</v>
       </c>
       <c r="R4" t="n">
-        <v>7205979</v>
+        <v>7205923</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113231545</v>
+        <v>113231513</v>
       </c>
       <c r="B5" t="n">
-        <v>79185</v>
+        <v>79197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546772</v>
+        <v>546603</v>
       </c>
       <c r="R5" t="n">
-        <v>7205856</v>
+        <v>7205952</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113231559</v>
+        <v>113231534</v>
       </c>
       <c r="B6" t="n">
-        <v>79218</v>
+        <v>79197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546819</v>
+        <v>546624</v>
       </c>
       <c r="R6" t="n">
-        <v>7205732</v>
+        <v>7205957</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113231551</v>
+        <v>113231555</v>
       </c>
       <c r="B7" t="n">
-        <v>56765</v>
+        <v>79197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,39 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546819</v>
+        <v>546821</v>
       </c>
       <c r="R7" t="n">
-        <v>7205844</v>
+        <v>7205745</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113231529</v>
+        <v>113231519</v>
       </c>
       <c r="B8" t="n">
-        <v>79185</v>
+        <v>90057</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546577</v>
+        <v>546487</v>
       </c>
       <c r="R8" t="n">
-        <v>7206034</v>
+        <v>7205984</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113231530</v>
+        <v>113231528</v>
       </c>
       <c r="B9" t="n">
-        <v>78121</v>
+        <v>90739</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,7 +1502,7 @@
         <v>546576</v>
       </c>
       <c r="R9" t="n">
-        <v>7206032</v>
+        <v>7206034</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1576,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113231513</v>
+        <v>113231514</v>
       </c>
       <c r="B10" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,7 +1611,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546603</v>
+        <v>546602</v>
       </c>
       <c r="R10" t="n">
         <v>7205952</v>
@@ -1688,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113231519</v>
+        <v>113231552</v>
       </c>
       <c r="B11" t="n">
-        <v>90045</v>
+        <v>78133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546487</v>
+        <v>546819</v>
       </c>
       <c r="R11" t="n">
-        <v>7205984</v>
+        <v>7205843</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113231537</v>
+        <v>113231536</v>
       </c>
       <c r="B12" t="n">
-        <v>79184</v>
+        <v>78133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546642</v>
+        <v>546624</v>
       </c>
       <c r="R12" t="n">
-        <v>7205923</v>
+        <v>7205956</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113231540</v>
+        <v>113231544</v>
       </c>
       <c r="B13" t="n">
-        <v>90063</v>
+        <v>78133</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546672</v>
+        <v>546727</v>
       </c>
       <c r="R13" t="n">
-        <v>7205887</v>
+        <v>7205919</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113231544</v>
+        <v>113231547</v>
       </c>
       <c r="B14" t="n">
-        <v>78121</v>
+        <v>74310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546727</v>
+        <v>546793</v>
       </c>
       <c r="R14" t="n">
-        <v>7205919</v>
+        <v>7205849</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113231556</v>
+        <v>113231525</v>
       </c>
       <c r="B15" t="n">
-        <v>56872</v>
+        <v>79223</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,38 +2147,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546836</v>
+        <v>546543</v>
       </c>
       <c r="R15" t="n">
-        <v>7205771</v>
+        <v>7206040</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113231536</v>
+        <v>113231559</v>
       </c>
       <c r="B16" t="n">
-        <v>78121</v>
+        <v>79230</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546624</v>
+        <v>546819</v>
       </c>
       <c r="R16" t="n">
-        <v>7205956</v>
+        <v>7205732</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113231552</v>
+        <v>113231518</v>
       </c>
       <c r="B17" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546819</v>
+        <v>546433</v>
       </c>
       <c r="R17" t="n">
-        <v>7205843</v>
+        <v>7205978</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113231561</v>
+        <v>113231556</v>
       </c>
       <c r="B18" t="n">
-        <v>74302</v>
+        <v>56873</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,38 +2479,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546831</v>
+        <v>546836</v>
       </c>
       <c r="R18" t="n">
-        <v>7205718</v>
+        <v>7205771</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2551,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113231527</v>
+        <v>113231557</v>
       </c>
       <c r="B19" t="n">
-        <v>79184</v>
+        <v>78133</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,21 +2599,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546542</v>
+        <v>546821</v>
       </c>
       <c r="R19" t="n">
-        <v>7206042</v>
+        <v>7205743</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113231549</v>
+        <v>113231550</v>
       </c>
       <c r="B20" t="n">
-        <v>56765</v>
+        <v>78133</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,36 +2711,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546817</v>
+        <v>546818</v>
       </c>
       <c r="R20" t="n">
         <v>7205855</v>
@@ -2817,10 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113231555</v>
+        <v>113231524</v>
       </c>
       <c r="B21" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,21 +2823,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2857,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546821</v>
+        <v>546496</v>
       </c>
       <c r="R21" t="n">
-        <v>7205745</v>
+        <v>7205951</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113231539</v>
+        <v>113231562</v>
       </c>
       <c r="B22" t="n">
-        <v>90387</v>
+        <v>90075</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,25 +2931,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546673</v>
+        <v>546830</v>
       </c>
       <c r="R22" t="n">
-        <v>7205890</v>
+        <v>7205715</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3004,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,10 +3031,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113231535</v>
+        <v>113231539</v>
       </c>
       <c r="B23" t="n">
-        <v>90605</v>
+        <v>90399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,21 +3047,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>760</v>
+        <v>2063</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3081,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546623</v>
+        <v>546673</v>
       </c>
       <c r="R23" t="n">
-        <v>7205959</v>
+        <v>7205890</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3116,7 +3106,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3126,7 +3116,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113231547</v>
+        <v>113231558</v>
       </c>
       <c r="B24" t="n">
-        <v>74298</v>
+        <v>79197</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,21 +3159,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +3183,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546793</v>
+        <v>546816</v>
       </c>
       <c r="R24" t="n">
-        <v>7205849</v>
+        <v>7205730</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3228,7 +3218,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3228,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,10 +3255,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113231546</v>
+        <v>113231785</v>
       </c>
       <c r="B25" t="n">
-        <v>78121</v>
+        <v>57363</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3277,38 +3267,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546772</v>
+        <v>546816</v>
       </c>
       <c r="R25" t="n">
-        <v>7205856</v>
+        <v>7205730</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3340,7 +3334,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3344,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113231531</v>
+        <v>113231538</v>
       </c>
       <c r="B26" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3393,21 +3387,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3417,10 +3411,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546605</v>
+        <v>546640</v>
       </c>
       <c r="R26" t="n">
-        <v>7206002</v>
+        <v>7205922</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3452,7 +3446,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3456,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,10 +3483,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113231526</v>
+        <v>113231553</v>
       </c>
       <c r="B27" t="n">
-        <v>79185</v>
+        <v>56766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3505,34 +3499,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546544</v>
+        <v>546814</v>
       </c>
       <c r="R27" t="n">
-        <v>7206041</v>
+        <v>7205823</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3564,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113231563</v>
+        <v>113231543</v>
       </c>
       <c r="B28" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3617,34 +3616,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546831</v>
+        <v>546727</v>
       </c>
       <c r="R28" t="n">
-        <v>7205718</v>
+        <v>7205919</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3676,7 +3680,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3686,7 +3690,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3713,10 +3717,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113231532</v>
+        <v>113231551</v>
       </c>
       <c r="B29" t="n">
-        <v>79218</v>
+        <v>56766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3725,38 +3729,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546604</v>
+        <v>546819</v>
       </c>
       <c r="R29" t="n">
-        <v>7206002</v>
+        <v>7205844</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3788,7 +3797,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3798,7 +3807,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3825,10 +3834,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113231542</v>
+        <v>113231533</v>
       </c>
       <c r="B30" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3841,21 +3850,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3865,10 +3874,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546717</v>
+        <v>546607</v>
       </c>
       <c r="R30" t="n">
-        <v>7205909</v>
+        <v>7206002</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3900,7 +3909,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3910,7 +3919,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3937,10 +3946,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113231785</v>
+        <v>113231532</v>
       </c>
       <c r="B31" t="n">
-        <v>57362</v>
+        <v>79230</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3949,42 +3958,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102125</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546816</v>
+        <v>546604</v>
       </c>
       <c r="R31" t="n">
-        <v>7205730</v>
+        <v>7206002</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4016,7 +4021,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4026,7 +4031,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4053,10 +4058,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113231521</v>
+        <v>113231549</v>
       </c>
       <c r="B32" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4069,34 +4074,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546488</v>
+        <v>546817</v>
       </c>
       <c r="R32" t="n">
-        <v>7205982</v>
+        <v>7205855</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4128,7 +4138,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4138,7 +4148,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,10 +4175,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113231538</v>
+        <v>113231526</v>
       </c>
       <c r="B33" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,21 +4191,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4205,10 +4215,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546640</v>
+        <v>546544</v>
       </c>
       <c r="R33" t="n">
-        <v>7205922</v>
+        <v>7206041</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4240,7 +4250,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4250,7 +4260,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4277,10 +4287,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113231533</v>
+        <v>113231545</v>
       </c>
       <c r="B34" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4293,21 +4303,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4317,10 +4327,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546607</v>
+        <v>546772</v>
       </c>
       <c r="R34" t="n">
-        <v>7206002</v>
+        <v>7205856</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4352,7 +4362,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4362,7 +4372,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4389,10 +4399,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113231525</v>
+        <v>113231529</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>79197</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4401,25 +4411,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4429,10 +4439,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546543</v>
+        <v>546577</v>
       </c>
       <c r="R35" t="n">
-        <v>7206040</v>
+        <v>7206034</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4464,7 +4474,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4474,7 +4484,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4501,10 +4511,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113231550</v>
+        <v>113231512</v>
       </c>
       <c r="B36" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4517,21 +4527,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4541,10 +4551,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546818</v>
+        <v>546610</v>
       </c>
       <c r="R36" t="n">
-        <v>7205855</v>
+        <v>7205953</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4576,7 +4586,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4586,7 +4596,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4613,10 +4623,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113231558</v>
+        <v>113231521</v>
       </c>
       <c r="B37" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4629,21 +4639,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4653,10 +4663,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546816</v>
+        <v>546488</v>
       </c>
       <c r="R37" t="n">
-        <v>7205730</v>
+        <v>7205982</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4688,7 +4698,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4698,7 +4708,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4725,10 +4735,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113231528</v>
+        <v>113231542</v>
       </c>
       <c r="B38" t="n">
-        <v>90727</v>
+        <v>79197</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4737,25 +4747,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4765,10 +4775,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546576</v>
+        <v>546717</v>
       </c>
       <c r="R38" t="n">
-        <v>7206034</v>
+        <v>7205909</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4800,7 +4810,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4810,7 +4820,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4837,10 +4847,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113231514</v>
+        <v>113231527</v>
       </c>
       <c r="B39" t="n">
-        <v>78121</v>
+        <v>79196</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4853,21 +4863,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4877,10 +4887,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546602</v>
+        <v>546542</v>
       </c>
       <c r="R39" t="n">
-        <v>7205952</v>
+        <v>7206042</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4912,7 +4922,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4922,7 +4932,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4949,10 +4959,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113231524</v>
+        <v>113231541</v>
       </c>
       <c r="B40" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4989,10 +4999,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546496</v>
+        <v>546672</v>
       </c>
       <c r="R40" t="n">
-        <v>7205951</v>
+        <v>7205887</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5024,7 +5034,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5034,7 +5044,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5061,10 +5071,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113231512</v>
+        <v>113231540</v>
       </c>
       <c r="B41" t="n">
-        <v>79185</v>
+        <v>90075</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5077,21 +5087,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5101,10 +5111,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546610</v>
+        <v>546672</v>
       </c>
       <c r="R41" t="n">
-        <v>7205953</v>
+        <v>7205887</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5136,7 +5146,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5146,7 +5156,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5173,10 +5183,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113231515</v>
+        <v>113231523</v>
       </c>
       <c r="B42" t="n">
-        <v>79185</v>
+        <v>56911</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5189,34 +5199,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546574</v>
+        <v>546496</v>
       </c>
       <c r="R42" t="n">
-        <v>7205984</v>
+        <v>7205950</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5248,7 +5267,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5258,7 +5277,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5285,10 +5304,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113231554</v>
+        <v>113231515</v>
       </c>
       <c r="B43" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5301,21 +5320,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5325,10 +5344,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546814</v>
+        <v>546574</v>
       </c>
       <c r="R43" t="n">
-        <v>7205823</v>
+        <v>7205984</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5360,7 +5379,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5370,7 +5389,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5397,10 +5416,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113231518</v>
+        <v>113231531</v>
       </c>
       <c r="B44" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5413,21 +5432,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5437,10 +5456,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546433</v>
+        <v>546605</v>
       </c>
       <c r="R44" t="n">
-        <v>7205978</v>
+        <v>7206002</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5472,7 +5491,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5482,7 +5501,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5509,10 +5528,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113231516</v>
+        <v>113231554</v>
       </c>
       <c r="B45" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5549,10 +5568,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546573</v>
+        <v>546814</v>
       </c>
       <c r="R45" t="n">
-        <v>7205984</v>
+        <v>7205823</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5584,7 +5603,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5594,7 +5613,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5621,10 +5640,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113231553</v>
+        <v>113231530</v>
       </c>
       <c r="B46" t="n">
-        <v>56765</v>
+        <v>78133</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5637,39 +5656,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546814</v>
+        <v>546576</v>
       </c>
       <c r="R46" t="n">
-        <v>7205823</v>
+        <v>7206032</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5701,7 +5715,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5711,7 +5725,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5738,10 +5752,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113231557</v>
+        <v>113231548</v>
       </c>
       <c r="B47" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5778,10 +5792,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546821</v>
+        <v>546793</v>
       </c>
       <c r="R47" t="n">
-        <v>7205743</v>
+        <v>7205849</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5813,7 +5827,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5823,7 +5837,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5850,10 +5864,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113231543</v>
+        <v>113231535</v>
       </c>
       <c r="B48" t="n">
-        <v>56765</v>
+        <v>90617</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5862,43 +5876,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546727</v>
+        <v>546623</v>
       </c>
       <c r="R48" t="n">
-        <v>7205919</v>
+        <v>7205959</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5930,7 +5939,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5940,7 +5949,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5967,10 +5976,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113231523</v>
+        <v>113231563</v>
       </c>
       <c r="B49" t="n">
-        <v>56910</v>
+        <v>78133</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5983,43 +5992,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546496</v>
+        <v>546831</v>
       </c>
       <c r="R49" t="n">
-        <v>7205950</v>
+        <v>7205718</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6088,10 +6088,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113231562</v>
+        <v>113231517</v>
       </c>
       <c r="B50" t="n">
-        <v>90063</v>
+        <v>74314</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546830</v>
+        <v>546435</v>
       </c>
       <c r="R50" t="n">
-        <v>7205715</v>
+        <v>7205979</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6200,10 +6200,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113231541</v>
+        <v>113231561</v>
       </c>
       <c r="B51" t="n">
-        <v>78121</v>
+        <v>74314</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6216,21 +6216,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6240,10 +6240,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546672</v>
+        <v>546831</v>
       </c>
       <c r="R51" t="n">
-        <v>7205887</v>
+        <v>7205718</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6315,7 +6315,7 @@
         <v>113231560</v>
       </c>
       <c r="B52" t="n">
-        <v>56910</v>
+        <v>56911</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113231546</v>
+        <v>113231537</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>79196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546772</v>
+        <v>546642</v>
       </c>
       <c r="R2" t="n">
-        <v>7205856</v>
+        <v>7205923</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113231516</v>
+        <v>113231560</v>
       </c>
       <c r="B3" t="n">
-        <v>78133</v>
+        <v>56911</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546573</v>
+        <v>546825</v>
       </c>
       <c r="R3" t="n">
-        <v>7205984</v>
+        <v>7205775</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113231537</v>
+        <v>113231512</v>
       </c>
       <c r="B4" t="n">
-        <v>79196</v>
+        <v>79197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546642</v>
+        <v>546610</v>
       </c>
       <c r="R4" t="n">
-        <v>7205923</v>
+        <v>7205953</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113231513</v>
+        <v>113231559</v>
       </c>
       <c r="B5" t="n">
-        <v>79197</v>
+        <v>79230</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546603</v>
+        <v>546819</v>
       </c>
       <c r="R5" t="n">
-        <v>7205952</v>
+        <v>7205732</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113231534</v>
+        <v>113231524</v>
       </c>
       <c r="B6" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546624</v>
+        <v>546496</v>
       </c>
       <c r="R6" t="n">
-        <v>7205957</v>
+        <v>7205951</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113231555</v>
+        <v>113231530</v>
       </c>
       <c r="B7" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546821</v>
+        <v>546576</v>
       </c>
       <c r="R7" t="n">
-        <v>7205745</v>
+        <v>7206032</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113231519</v>
+        <v>113231518</v>
       </c>
       <c r="B8" t="n">
-        <v>90057</v>
+        <v>78133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546487</v>
+        <v>546433</v>
       </c>
       <c r="R8" t="n">
-        <v>7205984</v>
+        <v>7205978</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113231528</v>
+        <v>113231519</v>
       </c>
       <c r="B9" t="n">
-        <v>90739</v>
+        <v>90057</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1475,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546576</v>
+        <v>546487</v>
       </c>
       <c r="R9" t="n">
-        <v>7206034</v>
+        <v>7205984</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,7 +1575,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113231514</v>
+        <v>113231533</v>
       </c>
       <c r="B10" t="n">
         <v>78133</v>
@@ -1611,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546602</v>
+        <v>546607</v>
       </c>
       <c r="R10" t="n">
-        <v>7205952</v>
+        <v>7206002</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113231552</v>
+        <v>113231562</v>
       </c>
       <c r="B11" t="n">
-        <v>78133</v>
+        <v>90075</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546819</v>
+        <v>546830</v>
       </c>
       <c r="R11" t="n">
-        <v>7205843</v>
+        <v>7205715</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113231536</v>
+        <v>113231534</v>
       </c>
       <c r="B12" t="n">
-        <v>78133</v>
+        <v>79197</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1815,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1838,7 +1842,7 @@
         <v>546624</v>
       </c>
       <c r="R12" t="n">
-        <v>7205956</v>
+        <v>7205957</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113231544</v>
+        <v>113231513</v>
       </c>
       <c r="B13" t="n">
-        <v>78133</v>
+        <v>79197</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1927,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546727</v>
+        <v>546603</v>
       </c>
       <c r="R13" t="n">
-        <v>7205919</v>
+        <v>7205952</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113231547</v>
+        <v>113231555</v>
       </c>
       <c r="B14" t="n">
-        <v>74310</v>
+        <v>79197</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546793</v>
+        <v>546821</v>
       </c>
       <c r="R14" t="n">
-        <v>7205849</v>
+        <v>7205745</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113231525</v>
+        <v>113231546</v>
       </c>
       <c r="B15" t="n">
-        <v>79223</v>
+        <v>78133</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2147,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546543</v>
+        <v>546772</v>
       </c>
       <c r="R15" t="n">
-        <v>7206040</v>
+        <v>7205856</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113231559</v>
+        <v>113231526</v>
       </c>
       <c r="B16" t="n">
-        <v>79230</v>
+        <v>79197</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2259,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546819</v>
+        <v>546544</v>
       </c>
       <c r="R16" t="n">
-        <v>7205732</v>
+        <v>7206041</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113231518</v>
+        <v>113231535</v>
       </c>
       <c r="B17" t="n">
-        <v>78133</v>
+        <v>90617</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2371,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546433</v>
+        <v>546623</v>
       </c>
       <c r="R17" t="n">
-        <v>7205978</v>
+        <v>7205959</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113231556</v>
+        <v>113231547</v>
       </c>
       <c r="B18" t="n">
-        <v>56873</v>
+        <v>74310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,42 +2483,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546836</v>
+        <v>546793</v>
       </c>
       <c r="R18" t="n">
-        <v>7205771</v>
+        <v>7205849</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113231557</v>
+        <v>113231561</v>
       </c>
       <c r="B19" t="n">
-        <v>78133</v>
+        <v>74314</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546821</v>
+        <v>546831</v>
       </c>
       <c r="R19" t="n">
-        <v>7205743</v>
+        <v>7205718</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113231550</v>
+        <v>113231553</v>
       </c>
       <c r="B20" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,34 +2711,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546818</v>
+        <v>546814</v>
       </c>
       <c r="R20" t="n">
-        <v>7205855</v>
+        <v>7205823</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2770,7 +2775,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2785,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113231524</v>
+        <v>113231551</v>
       </c>
       <c r="B21" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2823,34 +2828,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546496</v>
+        <v>546819</v>
       </c>
       <c r="R21" t="n">
-        <v>7205951</v>
+        <v>7205844</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,7 +2892,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2902,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113231562</v>
+        <v>113231531</v>
       </c>
       <c r="B22" t="n">
-        <v>90075</v>
+        <v>79197</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2935,21 +2945,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2959,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546830</v>
+        <v>546605</v>
       </c>
       <c r="R22" t="n">
-        <v>7205715</v>
+        <v>7206002</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2994,7 +3004,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,7 +3014,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,10 +3041,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113231539</v>
+        <v>113231514</v>
       </c>
       <c r="B23" t="n">
-        <v>90399</v>
+        <v>78133</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,25 +3053,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3081,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546673</v>
+        <v>546602</v>
       </c>
       <c r="R23" t="n">
-        <v>7205890</v>
+        <v>7205952</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3106,7 +3116,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3116,7 +3126,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,10 +3153,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113231558</v>
+        <v>113231548</v>
       </c>
       <c r="B24" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3159,21 +3169,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3183,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546816</v>
+        <v>546793</v>
       </c>
       <c r="R24" t="n">
-        <v>7205730</v>
+        <v>7205849</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3218,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3228,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3255,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113231785</v>
+        <v>113231543</v>
       </c>
       <c r="B25" t="n">
-        <v>57363</v>
+        <v>56766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,20 +3277,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3288,9 +3298,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>13</t>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3299,10 +3310,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546816</v>
+        <v>546727</v>
       </c>
       <c r="R25" t="n">
-        <v>7205730</v>
+        <v>7205919</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3334,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3344,7 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113231538</v>
+        <v>113231785</v>
       </c>
       <c r="B26" t="n">
-        <v>78133</v>
+        <v>57363</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3383,38 +3394,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546640</v>
+        <v>546816</v>
       </c>
       <c r="R26" t="n">
-        <v>7205922</v>
+        <v>7205730</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3446,7 +3461,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3471,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,10 +3498,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113231553</v>
+        <v>113231563</v>
       </c>
       <c r="B27" t="n">
-        <v>56766</v>
+        <v>78133</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3499,39 +3514,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546814</v>
+        <v>546831</v>
       </c>
       <c r="R27" t="n">
-        <v>7205823</v>
+        <v>7205718</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3563,7 +3573,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3583,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,10 +3610,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113231543</v>
+        <v>113231527</v>
       </c>
       <c r="B28" t="n">
-        <v>56766</v>
+        <v>79196</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3616,39 +3626,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546727</v>
+        <v>546542</v>
       </c>
       <c r="R28" t="n">
-        <v>7205919</v>
+        <v>7206042</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3680,7 +3685,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3690,7 +3695,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3717,10 +3722,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113231551</v>
+        <v>113231539</v>
       </c>
       <c r="B29" t="n">
-        <v>56766</v>
+        <v>90399</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3729,43 +3734,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546819</v>
+        <v>546673</v>
       </c>
       <c r="R29" t="n">
-        <v>7205844</v>
+        <v>7205890</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3834,7 +3834,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113231533</v>
+        <v>113231536</v>
       </c>
       <c r="B30" t="n">
         <v>78133</v>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546607</v>
+        <v>546624</v>
       </c>
       <c r="R30" t="n">
-        <v>7206002</v>
+        <v>7205956</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,10 +3946,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113231532</v>
+        <v>113231541</v>
       </c>
       <c r="B31" t="n">
-        <v>79230</v>
+        <v>78133</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3958,25 +3958,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546604</v>
+        <v>546672</v>
       </c>
       <c r="R31" t="n">
-        <v>7206002</v>
+        <v>7205887</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4058,10 +4058,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113231549</v>
+        <v>113231556</v>
       </c>
       <c r="B32" t="n">
-        <v>56766</v>
+        <v>56873</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4070,20 +4070,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4091,10 +4091,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4103,10 +4102,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546817</v>
+        <v>546836</v>
       </c>
       <c r="R32" t="n">
-        <v>7205855</v>
+        <v>7205771</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4138,7 +4137,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4148,7 +4147,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4175,7 +4174,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113231526</v>
+        <v>113231545</v>
       </c>
       <c r="B33" t="n">
         <v>79197</v>
@@ -4215,10 +4214,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546544</v>
+        <v>546772</v>
       </c>
       <c r="R33" t="n">
-        <v>7206041</v>
+        <v>7205856</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4250,7 +4249,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4260,7 +4259,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4287,7 +4286,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113231545</v>
+        <v>113231529</v>
       </c>
       <c r="B34" t="n">
         <v>79197</v>
@@ -4327,10 +4326,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546772</v>
+        <v>546577</v>
       </c>
       <c r="R34" t="n">
-        <v>7205856</v>
+        <v>7206034</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4362,7 +4361,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4372,7 +4371,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4399,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113231529</v>
+        <v>113231554</v>
       </c>
       <c r="B35" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4415,21 +4414,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4439,10 +4438,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546577</v>
+        <v>546814</v>
       </c>
       <c r="R35" t="n">
-        <v>7206034</v>
+        <v>7205823</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4474,7 +4473,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4484,7 +4483,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,10 +4510,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113231512</v>
+        <v>113231523</v>
       </c>
       <c r="B36" t="n">
-        <v>79197</v>
+        <v>56911</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4527,34 +4526,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546610</v>
+        <v>546496</v>
       </c>
       <c r="R36" t="n">
-        <v>7205953</v>
+        <v>7205950</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4586,7 +4594,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4596,7 +4604,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4623,10 +4631,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113231521</v>
+        <v>113231549</v>
       </c>
       <c r="B37" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4639,34 +4647,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546488</v>
+        <v>546817</v>
       </c>
       <c r="R37" t="n">
-        <v>7205982</v>
+        <v>7205855</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4698,7 +4711,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4708,7 +4721,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4735,7 +4748,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113231542</v>
+        <v>113231558</v>
       </c>
       <c r="B38" t="n">
         <v>79197</v>
@@ -4775,10 +4788,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546717</v>
+        <v>546816</v>
       </c>
       <c r="R38" t="n">
-        <v>7205909</v>
+        <v>7205730</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4810,7 +4823,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4820,7 +4833,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4847,10 +4860,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113231527</v>
+        <v>113231532</v>
       </c>
       <c r="B39" t="n">
-        <v>79196</v>
+        <v>79230</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4859,25 +4872,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4887,10 +4900,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546542</v>
+        <v>546604</v>
       </c>
       <c r="R39" t="n">
-        <v>7206042</v>
+        <v>7206002</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4922,7 +4935,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4932,7 +4945,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4959,7 +4972,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113231541</v>
+        <v>113231557</v>
       </c>
       <c r="B40" t="n">
         <v>78133</v>
@@ -4999,10 +5012,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546672</v>
+        <v>546821</v>
       </c>
       <c r="R40" t="n">
-        <v>7205887</v>
+        <v>7205743</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5034,7 +5047,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5044,7 +5057,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5071,10 +5084,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113231540</v>
+        <v>113231517</v>
       </c>
       <c r="B41" t="n">
-        <v>90075</v>
+        <v>74314</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5087,21 +5100,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5111,10 +5124,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546672</v>
+        <v>546435</v>
       </c>
       <c r="R41" t="n">
-        <v>7205887</v>
+        <v>7205979</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5146,7 +5159,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5156,7 +5169,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5183,10 +5196,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113231523</v>
+        <v>113231528</v>
       </c>
       <c r="B42" t="n">
-        <v>56911</v>
+        <v>90739</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5195,47 +5208,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546496</v>
+        <v>546576</v>
       </c>
       <c r="R42" t="n">
-        <v>7205950</v>
+        <v>7206034</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5267,7 +5271,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5277,7 +5281,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5304,10 +5308,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113231515</v>
+        <v>113231550</v>
       </c>
       <c r="B43" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5320,21 +5324,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5344,10 +5348,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546574</v>
+        <v>546818</v>
       </c>
       <c r="R43" t="n">
-        <v>7205984</v>
+        <v>7205855</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5379,7 +5383,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5389,7 +5393,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5416,10 +5420,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113231531</v>
+        <v>113231552</v>
       </c>
       <c r="B44" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5432,21 +5436,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5456,10 +5460,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546605</v>
+        <v>546819</v>
       </c>
       <c r="R44" t="n">
-        <v>7206002</v>
+        <v>7205843</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5491,7 +5495,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5501,7 +5505,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5528,7 +5532,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113231554</v>
+        <v>113231544</v>
       </c>
       <c r="B45" t="n">
         <v>78133</v>
@@ -5568,10 +5572,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546814</v>
+        <v>546727</v>
       </c>
       <c r="R45" t="n">
-        <v>7205823</v>
+        <v>7205919</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5603,7 +5607,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5613,7 +5617,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5640,7 +5644,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113231530</v>
+        <v>113231521</v>
       </c>
       <c r="B46" t="n">
         <v>78133</v>
@@ -5680,10 +5684,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546576</v>
+        <v>546488</v>
       </c>
       <c r="R46" t="n">
-        <v>7206032</v>
+        <v>7205982</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5715,7 +5719,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5725,7 +5729,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5752,10 +5756,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113231548</v>
+        <v>113231542</v>
       </c>
       <c r="B47" t="n">
-        <v>78133</v>
+        <v>79197</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5768,21 +5772,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5792,10 +5796,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546793</v>
+        <v>546717</v>
       </c>
       <c r="R47" t="n">
-        <v>7205849</v>
+        <v>7205909</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5827,7 +5831,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5837,7 +5841,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5864,10 +5868,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113231535</v>
+        <v>113231515</v>
       </c>
       <c r="B48" t="n">
-        <v>90617</v>
+        <v>79197</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5876,25 +5880,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5904,10 +5908,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546623</v>
+        <v>546574</v>
       </c>
       <c r="R48" t="n">
-        <v>7205959</v>
+        <v>7205984</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5939,7 +5943,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5949,7 +5953,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5976,10 +5980,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113231563</v>
+        <v>113231540</v>
       </c>
       <c r="B49" t="n">
-        <v>78133</v>
+        <v>90075</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5992,21 +5996,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6016,10 +6020,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546831</v>
+        <v>546672</v>
       </c>
       <c r="R49" t="n">
-        <v>7205718</v>
+        <v>7205887</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6051,7 +6055,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6061,7 +6065,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6088,10 +6092,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113231517</v>
+        <v>113231538</v>
       </c>
       <c r="B50" t="n">
-        <v>74314</v>
+        <v>78133</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6104,21 +6108,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6128,10 +6132,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546435</v>
+        <v>546640</v>
       </c>
       <c r="R50" t="n">
-        <v>7205979</v>
+        <v>7205922</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6163,7 +6167,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6173,7 +6177,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6200,10 +6204,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113231561</v>
+        <v>113231516</v>
       </c>
       <c r="B51" t="n">
-        <v>74314</v>
+        <v>78133</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6216,21 +6220,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6240,10 +6244,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546831</v>
+        <v>546573</v>
       </c>
       <c r="R51" t="n">
-        <v>7205718</v>
+        <v>7205984</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6275,7 +6279,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6285,7 +6289,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6312,10 +6316,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113231560</v>
+        <v>113231525</v>
       </c>
       <c r="B52" t="n">
-        <v>56911</v>
+        <v>79223</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6324,42 +6328,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546825</v>
+        <v>546543</v>
       </c>
       <c r="R52" t="n">
-        <v>7205775</v>
+        <v>7206040</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113231519</v>
+        <v>113231562</v>
       </c>
       <c r="B9" t="n">
-        <v>90057</v>
+        <v>90075</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1479,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546487</v>
+        <v>546830</v>
       </c>
       <c r="R9" t="n">
-        <v>7205984</v>
+        <v>7205715</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113231533</v>
+        <v>113231519</v>
       </c>
       <c r="B10" t="n">
-        <v>78133</v>
+        <v>90057</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546607</v>
+        <v>546487</v>
       </c>
       <c r="R10" t="n">
-        <v>7206002</v>
+        <v>7205984</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113231562</v>
+        <v>113231533</v>
       </c>
       <c r="B11" t="n">
-        <v>90075</v>
+        <v>78133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546830</v>
+        <v>546607</v>
       </c>
       <c r="R11" t="n">
-        <v>7205715</v>
+        <v>7206002</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2135,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113231546</v>
+        <v>113231535</v>
       </c>
       <c r="B15" t="n">
-        <v>78133</v>
+        <v>90617</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,25 +2147,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546772</v>
+        <v>546623</v>
       </c>
       <c r="R15" t="n">
-        <v>7205856</v>
+        <v>7205959</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113231535</v>
+        <v>113231546</v>
       </c>
       <c r="B17" t="n">
-        <v>90617</v>
+        <v>78133</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,25 +2371,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546623</v>
+        <v>546772</v>
       </c>
       <c r="R17" t="n">
-        <v>7205959</v>
+        <v>7205856</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113231531</v>
+        <v>113231785</v>
       </c>
       <c r="B22" t="n">
-        <v>79197</v>
+        <v>57363</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,38 +2941,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>102125</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546605</v>
+        <v>546816</v>
       </c>
       <c r="R22" t="n">
-        <v>7206002</v>
+        <v>7205730</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3004,7 +3008,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +3018,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,10 +3045,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113231514</v>
+        <v>113231543</v>
       </c>
       <c r="B23" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,34 +3061,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546602</v>
+        <v>546727</v>
       </c>
       <c r="R23" t="n">
-        <v>7205952</v>
+        <v>7205919</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3116,7 +3125,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3126,7 +3135,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,10 +3162,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113231548</v>
+        <v>113231531</v>
       </c>
       <c r="B24" t="n">
-        <v>78133</v>
+        <v>79197</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,21 +3178,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +3202,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546793</v>
+        <v>546605</v>
       </c>
       <c r="R24" t="n">
-        <v>7205849</v>
+        <v>7206002</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3228,7 +3237,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3247,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,10 +3274,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113231543</v>
+        <v>113231514</v>
       </c>
       <c r="B25" t="n">
-        <v>56766</v>
+        <v>78133</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,39 +3290,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546727</v>
+        <v>546602</v>
       </c>
       <c r="R25" t="n">
-        <v>7205919</v>
+        <v>7205952</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,7 +3349,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3359,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,10 +3386,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113231785</v>
+        <v>113231548</v>
       </c>
       <c r="B26" t="n">
-        <v>57363</v>
+        <v>78133</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3394,42 +3398,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546816</v>
+        <v>546793</v>
       </c>
       <c r="R26" t="n">
-        <v>7205730</v>
+        <v>7205849</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4860,10 +4860,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113231532</v>
+        <v>113231557</v>
       </c>
       <c r="B39" t="n">
-        <v>79230</v>
+        <v>78133</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4872,25 +4872,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4900,10 +4900,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546604</v>
+        <v>546821</v>
       </c>
       <c r="R39" t="n">
-        <v>7206002</v>
+        <v>7205743</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4972,10 +4972,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113231557</v>
+        <v>113231517</v>
       </c>
       <c r="B40" t="n">
-        <v>78133</v>
+        <v>74314</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4988,21 +4988,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546821</v>
+        <v>546435</v>
       </c>
       <c r="R40" t="n">
-        <v>7205743</v>
+        <v>7205979</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5084,10 +5084,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113231517</v>
+        <v>113231532</v>
       </c>
       <c r="B41" t="n">
-        <v>74314</v>
+        <v>79230</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5096,25 +5096,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546435</v>
+        <v>546604</v>
       </c>
       <c r="R41" t="n">
-        <v>7205979</v>
+        <v>7206002</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6092,10 +6092,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113231538</v>
+        <v>113231525</v>
       </c>
       <c r="B50" t="n">
-        <v>78133</v>
+        <v>79223</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6104,25 +6104,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546640</v>
+        <v>546543</v>
       </c>
       <c r="R50" t="n">
-        <v>7205922</v>
+        <v>7206040</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6204,7 +6204,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113231516</v>
+        <v>113231538</v>
       </c>
       <c r="B51" t="n">
         <v>78133</v>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546573</v>
+        <v>546640</v>
       </c>
       <c r="R51" t="n">
-        <v>7205984</v>
+        <v>7205922</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6316,10 +6316,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113231525</v>
+        <v>113231516</v>
       </c>
       <c r="B52" t="n">
-        <v>79223</v>
+        <v>78133</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6328,25 +6328,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546543</v>
+        <v>546573</v>
       </c>
       <c r="R52" t="n">
-        <v>7206040</v>
+        <v>7205984</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113231537</v>
+        <v>113231548</v>
       </c>
       <c r="B2" t="n">
-        <v>79196</v>
+        <v>78155</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546642</v>
+        <v>546793</v>
       </c>
       <c r="R2" t="n">
-        <v>7205923</v>
+        <v>7205849</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113231560</v>
+        <v>113231532</v>
       </c>
       <c r="B3" t="n">
-        <v>56911</v>
+        <v>79252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546825</v>
+        <v>546604</v>
       </c>
       <c r="R3" t="n">
-        <v>7205775</v>
+        <v>7206002</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113231512</v>
+        <v>113231563</v>
       </c>
       <c r="B4" t="n">
-        <v>79197</v>
+        <v>78155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546610</v>
+        <v>546831</v>
       </c>
       <c r="R4" t="n">
-        <v>7205953</v>
+        <v>7205718</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113231559</v>
+        <v>113231512</v>
       </c>
       <c r="B5" t="n">
-        <v>79230</v>
+        <v>79219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546819</v>
+        <v>546610</v>
       </c>
       <c r="R5" t="n">
-        <v>7205732</v>
+        <v>7205953</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113231524</v>
+        <v>113231527</v>
       </c>
       <c r="B6" t="n">
-        <v>78133</v>
+        <v>79218</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546496</v>
+        <v>546542</v>
       </c>
       <c r="R6" t="n">
-        <v>7205951</v>
+        <v>7206042</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113231530</v>
+        <v>113231515</v>
       </c>
       <c r="B7" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546576</v>
+        <v>546574</v>
       </c>
       <c r="R7" t="n">
-        <v>7206032</v>
+        <v>7205984</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113231518</v>
+        <v>113231530</v>
       </c>
       <c r="B8" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546433</v>
+        <v>546576</v>
       </c>
       <c r="R8" t="n">
-        <v>7205978</v>
+        <v>7206032</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1426,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113231562</v>
+        <v>113231550</v>
       </c>
       <c r="B9" t="n">
-        <v>90075</v>
+        <v>78155</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546830</v>
+        <v>546818</v>
       </c>
       <c r="R9" t="n">
-        <v>7205715</v>
+        <v>7205855</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1538,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113231519</v>
+        <v>113231554</v>
       </c>
       <c r="B10" t="n">
-        <v>90057</v>
+        <v>78155</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546487</v>
+        <v>546814</v>
       </c>
       <c r="R10" t="n">
-        <v>7205984</v>
+        <v>7205823</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113231533</v>
+        <v>113231553</v>
       </c>
       <c r="B11" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,34 +1699,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546607</v>
+        <v>546814</v>
       </c>
       <c r="R11" t="n">
-        <v>7206002</v>
+        <v>7205823</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113231534</v>
+        <v>113231551</v>
       </c>
       <c r="B12" t="n">
-        <v>79197</v>
+        <v>56766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,34 +1816,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546624</v>
+        <v>546819</v>
       </c>
       <c r="R12" t="n">
-        <v>7205957</v>
+        <v>7205844</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1874,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113231513</v>
+        <v>113231556</v>
       </c>
       <c r="B13" t="n">
-        <v>79197</v>
+        <v>56873</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,38 +1929,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546603</v>
+        <v>546836</v>
       </c>
       <c r="R13" t="n">
-        <v>7205952</v>
+        <v>7205771</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1986,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113231555</v>
+        <v>113231536</v>
       </c>
       <c r="B14" t="n">
-        <v>79197</v>
+        <v>78155</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546821</v>
+        <v>546624</v>
       </c>
       <c r="R14" t="n">
-        <v>7205745</v>
+        <v>7205956</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2098,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113231535</v>
+        <v>113231521</v>
       </c>
       <c r="B15" t="n">
-        <v>90617</v>
+        <v>78155</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,25 +2157,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546623</v>
+        <v>546488</v>
       </c>
       <c r="R15" t="n">
-        <v>7205959</v>
+        <v>7205982</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2210,7 +2220,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2230,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,10 +2257,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113231526</v>
+        <v>113231552</v>
       </c>
       <c r="B16" t="n">
-        <v>79197</v>
+        <v>78155</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,21 +2273,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2287,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546544</v>
+        <v>546819</v>
       </c>
       <c r="R16" t="n">
-        <v>7206041</v>
+        <v>7205843</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2322,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,10 +2369,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113231546</v>
+        <v>113231558</v>
       </c>
       <c r="B17" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,21 +2385,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546772</v>
+        <v>546816</v>
       </c>
       <c r="R17" t="n">
-        <v>7205856</v>
+        <v>7205730</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,10 +2481,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113231547</v>
+        <v>113231545</v>
       </c>
       <c r="B18" t="n">
-        <v>74310</v>
+        <v>79219</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2487,21 +2497,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2521,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546793</v>
+        <v>546772</v>
       </c>
       <c r="R18" t="n">
-        <v>7205849</v>
+        <v>7205856</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2556,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2566,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113231561</v>
+        <v>113231541</v>
       </c>
       <c r="B19" t="n">
-        <v>74314</v>
+        <v>78155</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,21 +2609,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546831</v>
+        <v>546672</v>
       </c>
       <c r="R19" t="n">
-        <v>7205718</v>
+        <v>7205887</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2678,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113231553</v>
+        <v>113231518</v>
       </c>
       <c r="B20" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,39 +2721,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546814</v>
+        <v>546433</v>
       </c>
       <c r="R20" t="n">
-        <v>7205823</v>
+        <v>7205978</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2775,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2785,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113231551</v>
+        <v>113231561</v>
       </c>
       <c r="B21" t="n">
-        <v>56766</v>
+        <v>74336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2828,39 +2833,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546819</v>
+        <v>546831</v>
       </c>
       <c r="R21" t="n">
-        <v>7205844</v>
+        <v>7205718</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113231785</v>
+        <v>113231535</v>
       </c>
       <c r="B22" t="n">
-        <v>57363</v>
+        <v>90639</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2945,38 +2945,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102125</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546816</v>
+        <v>546623</v>
       </c>
       <c r="R22" t="n">
-        <v>7205730</v>
+        <v>7205959</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3008,7 +3004,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3018,7 +3014,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,10 +3041,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113231543</v>
+        <v>113231528</v>
       </c>
       <c r="B23" t="n">
-        <v>56766</v>
+        <v>90761</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,43 +3053,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546727</v>
+        <v>546576</v>
       </c>
       <c r="R23" t="n">
-        <v>7205919</v>
+        <v>7206034</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3125,7 +3116,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3135,7 +3126,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,10 +3153,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113231531</v>
+        <v>113231562</v>
       </c>
       <c r="B24" t="n">
-        <v>79197</v>
+        <v>90097</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3178,21 +3169,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3202,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546605</v>
+        <v>546830</v>
       </c>
       <c r="R24" t="n">
-        <v>7206002</v>
+        <v>7205715</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3237,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3247,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3274,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113231514</v>
+        <v>113231549</v>
       </c>
       <c r="B25" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3290,34 +3281,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546602</v>
+        <v>546817</v>
       </c>
       <c r="R25" t="n">
-        <v>7205952</v>
+        <v>7205855</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3349,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3359,7 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3386,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113231548</v>
+        <v>113231547</v>
       </c>
       <c r="B26" t="n">
-        <v>78133</v>
+        <v>74332</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3402,21 +3398,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3461,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3471,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3498,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113231563</v>
+        <v>113231560</v>
       </c>
       <c r="B27" t="n">
-        <v>78133</v>
+        <v>56911</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3514,34 +3510,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546831</v>
+        <v>546825</v>
       </c>
       <c r="R27" t="n">
-        <v>7205718</v>
+        <v>7205775</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3610,10 +3610,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113231527</v>
+        <v>113231526</v>
       </c>
       <c r="B28" t="n">
-        <v>79196</v>
+        <v>79219</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3626,21 +3626,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546542</v>
+        <v>546544</v>
       </c>
       <c r="R28" t="n">
-        <v>7206042</v>
+        <v>7206041</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3722,10 +3722,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113231539</v>
+        <v>113231531</v>
       </c>
       <c r="B29" t="n">
-        <v>90399</v>
+        <v>79219</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3734,25 +3734,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546673</v>
+        <v>546605</v>
       </c>
       <c r="R29" t="n">
-        <v>7205890</v>
+        <v>7206002</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3834,10 +3834,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113231536</v>
+        <v>113231523</v>
       </c>
       <c r="B30" t="n">
-        <v>78133</v>
+        <v>56911</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3850,34 +3850,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546624</v>
+        <v>546496</v>
       </c>
       <c r="R30" t="n">
-        <v>7205956</v>
+        <v>7205950</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3909,7 +3918,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3919,7 +3928,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,10 +3955,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113231541</v>
+        <v>113231542</v>
       </c>
       <c r="B31" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3962,21 +3971,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3986,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546672</v>
+        <v>546717</v>
       </c>
       <c r="R31" t="n">
-        <v>7205887</v>
+        <v>7205909</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4021,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4031,7 +4040,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4058,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113231556</v>
+        <v>113231517</v>
       </c>
       <c r="B32" t="n">
-        <v>56873</v>
+        <v>74336</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4070,42 +4079,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546836</v>
+        <v>546435</v>
       </c>
       <c r="R32" t="n">
-        <v>7205771</v>
+        <v>7205979</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4137,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,7 +4152,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4174,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113231545</v>
+        <v>113231525</v>
       </c>
       <c r="B33" t="n">
-        <v>79197</v>
+        <v>79245</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4186,25 +4191,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4214,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546772</v>
+        <v>546543</v>
       </c>
       <c r="R33" t="n">
-        <v>7205856</v>
+        <v>7206040</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4249,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4259,7 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4286,10 +4291,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113231529</v>
+        <v>113231540</v>
       </c>
       <c r="B34" t="n">
-        <v>79197</v>
+        <v>90097</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4302,21 +4307,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4326,10 +4331,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546577</v>
+        <v>546672</v>
       </c>
       <c r="R34" t="n">
-        <v>7206034</v>
+        <v>7205887</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4361,7 +4366,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4371,7 +4376,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4398,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113231554</v>
+        <v>113231544</v>
       </c>
       <c r="B35" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4438,10 +4443,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546814</v>
+        <v>546727</v>
       </c>
       <c r="R35" t="n">
-        <v>7205823</v>
+        <v>7205919</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4473,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4483,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4510,10 +4515,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113231523</v>
+        <v>113231533</v>
       </c>
       <c r="B36" t="n">
-        <v>56911</v>
+        <v>78155</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4526,43 +4531,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546496</v>
+        <v>546607</v>
       </c>
       <c r="R36" t="n">
-        <v>7205950</v>
+        <v>7206002</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4594,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4604,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4631,10 +4627,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113231549</v>
+        <v>113231516</v>
       </c>
       <c r="B37" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4647,39 +4643,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546817</v>
+        <v>546573</v>
       </c>
       <c r="R37" t="n">
-        <v>7205855</v>
+        <v>7205984</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4711,7 +4702,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4721,7 +4712,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4748,10 +4739,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113231558</v>
+        <v>113231555</v>
       </c>
       <c r="B38" t="n">
-        <v>79197</v>
+        <v>79219</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4788,10 +4779,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546816</v>
+        <v>546821</v>
       </c>
       <c r="R38" t="n">
-        <v>7205730</v>
+        <v>7205745</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4823,7 +4814,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4833,7 +4824,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4860,10 +4851,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113231557</v>
+        <v>113231534</v>
       </c>
       <c r="B39" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4876,21 +4867,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4900,10 +4891,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546821</v>
+        <v>546624</v>
       </c>
       <c r="R39" t="n">
-        <v>7205743</v>
+        <v>7205957</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4935,7 +4926,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4945,7 +4936,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4972,10 +4963,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113231517</v>
+        <v>113231513</v>
       </c>
       <c r="B40" t="n">
-        <v>74314</v>
+        <v>79219</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4988,21 +4979,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5012,10 +5003,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546435</v>
+        <v>546603</v>
       </c>
       <c r="R40" t="n">
-        <v>7205979</v>
+        <v>7205952</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5047,7 +5038,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5057,7 +5048,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5084,10 +5075,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113231532</v>
+        <v>113231529</v>
       </c>
       <c r="B41" t="n">
-        <v>79230</v>
+        <v>79219</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5096,25 +5087,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5124,10 +5115,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546604</v>
+        <v>546577</v>
       </c>
       <c r="R41" t="n">
-        <v>7206002</v>
+        <v>7206034</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5159,7 +5150,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5169,7 +5160,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5196,10 +5187,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113231528</v>
+        <v>113231785</v>
       </c>
       <c r="B42" t="n">
-        <v>90739</v>
+        <v>57363</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5208,38 +5199,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>102125</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546576</v>
+        <v>546816</v>
       </c>
       <c r="R42" t="n">
-        <v>7206034</v>
+        <v>7205730</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5271,7 +5266,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5281,7 +5276,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5308,10 +5303,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113231550</v>
+        <v>113231537</v>
       </c>
       <c r="B43" t="n">
-        <v>78133</v>
+        <v>79218</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5324,21 +5319,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5348,10 +5343,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546818</v>
+        <v>546642</v>
       </c>
       <c r="R43" t="n">
-        <v>7205855</v>
+        <v>7205923</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5383,7 +5378,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5393,7 +5388,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5420,10 +5415,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113231552</v>
+        <v>113231559</v>
       </c>
       <c r="B44" t="n">
-        <v>78133</v>
+        <v>79252</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5432,25 +5427,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5463,7 +5458,7 @@
         <v>546819</v>
       </c>
       <c r="R44" t="n">
-        <v>7205843</v>
+        <v>7205732</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5495,7 +5490,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5505,7 +5500,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5532,10 +5527,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113231544</v>
+        <v>113231546</v>
       </c>
       <c r="B45" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5572,10 +5567,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546727</v>
+        <v>546772</v>
       </c>
       <c r="R45" t="n">
-        <v>7205919</v>
+        <v>7205856</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5607,7 +5602,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5617,7 +5612,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5644,10 +5639,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113231521</v>
+        <v>113231543</v>
       </c>
       <c r="B46" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5660,34 +5655,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546488</v>
+        <v>546727</v>
       </c>
       <c r="R46" t="n">
-        <v>7205982</v>
+        <v>7205919</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5756,10 +5756,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113231542</v>
+        <v>113231519</v>
       </c>
       <c r="B47" t="n">
-        <v>79197</v>
+        <v>90079</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5772,21 +5772,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546717</v>
+        <v>546487</v>
       </c>
       <c r="R47" t="n">
-        <v>7205909</v>
+        <v>7205984</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5868,10 +5868,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113231515</v>
+        <v>113231539</v>
       </c>
       <c r="B48" t="n">
-        <v>79197</v>
+        <v>90421</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5880,25 +5880,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546574</v>
+        <v>546673</v>
       </c>
       <c r="R48" t="n">
-        <v>7205984</v>
+        <v>7205890</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5980,10 +5980,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113231540</v>
+        <v>113231524</v>
       </c>
       <c r="B49" t="n">
-        <v>90075</v>
+        <v>78155</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5996,21 +5996,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546672</v>
+        <v>546496</v>
       </c>
       <c r="R49" t="n">
-        <v>7205887</v>
+        <v>7205951</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6092,10 +6092,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113231525</v>
+        <v>113231557</v>
       </c>
       <c r="B50" t="n">
-        <v>79223</v>
+        <v>78155</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6104,25 +6104,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546543</v>
+        <v>546821</v>
       </c>
       <c r="R50" t="n">
-        <v>7206040</v>
+        <v>7205743</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6204,10 +6204,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113231538</v>
+        <v>113231514</v>
       </c>
       <c r="B51" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546640</v>
+        <v>546602</v>
       </c>
       <c r="R51" t="n">
-        <v>7205922</v>
+        <v>7205952</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6316,10 +6316,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113231516</v>
+        <v>113231538</v>
       </c>
       <c r="B52" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546573</v>
+        <v>546640</v>
       </c>
       <c r="R52" t="n">
-        <v>7205984</v>
+        <v>7205922</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -2369,10 +2369,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113231558</v>
+        <v>113231541</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>78155</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546816</v>
+        <v>546672</v>
       </c>
       <c r="R17" t="n">
-        <v>7205730</v>
+        <v>7205887</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2593,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113231541</v>
+        <v>113231558</v>
       </c>
       <c r="B19" t="n">
-        <v>78155</v>
+        <v>79219</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2609,21 +2609,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546672</v>
+        <v>546816</v>
       </c>
       <c r="R19" t="n">
-        <v>7205887</v>
+        <v>7205730</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113231547</v>
+        <v>113231560</v>
       </c>
       <c r="B26" t="n">
-        <v>74332</v>
+        <v>56911</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3398,34 +3398,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>310</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546793</v>
+        <v>546825</v>
       </c>
       <c r="R26" t="n">
-        <v>7205849</v>
+        <v>7205775</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3457,7 +3461,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3471,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3498,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113231560</v>
+        <v>113231547</v>
       </c>
       <c r="B27" t="n">
-        <v>56911</v>
+        <v>74332</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,38 +3514,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546825</v>
+        <v>546793</v>
       </c>
       <c r="R27" t="n">
-        <v>7205775</v>
+        <v>7205849</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113231540</v>
+        <v>113231544</v>
       </c>
       <c r="B34" t="n">
-        <v>90097</v>
+        <v>78155</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546672</v>
+        <v>546727</v>
       </c>
       <c r="R34" t="n">
-        <v>7205887</v>
+        <v>7205919</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4403,7 +4403,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113231544</v>
+        <v>113231533</v>
       </c>
       <c r="B35" t="n">
         <v>78155</v>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546727</v>
+        <v>546607</v>
       </c>
       <c r="R35" t="n">
-        <v>7205919</v>
+        <v>7206002</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,7 +4515,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113231533</v>
+        <v>113231516</v>
       </c>
       <c r="B36" t="n">
         <v>78155</v>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546607</v>
+        <v>546573</v>
       </c>
       <c r="R36" t="n">
-        <v>7206002</v>
+        <v>7205984</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4627,10 +4627,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113231516</v>
+        <v>113231540</v>
       </c>
       <c r="B37" t="n">
-        <v>78155</v>
+        <v>90097</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546573</v>
+        <v>546672</v>
       </c>
       <c r="R37" t="n">
-        <v>7205984</v>
+        <v>7205887</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113231548</v>
+        <v>113231528</v>
       </c>
       <c r="B2" t="n">
-        <v>78155</v>
+        <v>90765</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546793</v>
+        <v>546576</v>
       </c>
       <c r="R2" t="n">
-        <v>7205849</v>
+        <v>7206034</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113231532</v>
+        <v>113231537</v>
       </c>
       <c r="B3" t="n">
-        <v>79252</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546604</v>
+        <v>546642</v>
       </c>
       <c r="R3" t="n">
-        <v>7206002</v>
+        <v>7205923</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113231563</v>
+        <v>113231523</v>
       </c>
       <c r="B4" t="n">
-        <v>78155</v>
+        <v>56914</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546831</v>
+        <v>546496</v>
       </c>
       <c r="R4" t="n">
-        <v>7205718</v>
+        <v>7205950</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113231512</v>
+        <v>113231517</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>74339</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546610</v>
+        <v>546435</v>
       </c>
       <c r="R5" t="n">
-        <v>7205953</v>
+        <v>7205979</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113231527</v>
+        <v>113231553</v>
       </c>
       <c r="B6" t="n">
-        <v>79218</v>
+        <v>56769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1148,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546542</v>
+        <v>546814</v>
       </c>
       <c r="R6" t="n">
-        <v>7206042</v>
+        <v>7205823</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113231515</v>
+        <v>113231527</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546574</v>
+        <v>546542</v>
       </c>
       <c r="R7" t="n">
-        <v>7205984</v>
+        <v>7206042</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113231530</v>
+        <v>113231556</v>
       </c>
       <c r="B8" t="n">
-        <v>78155</v>
+        <v>56876</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,38 +1373,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546576</v>
+        <v>546836</v>
       </c>
       <c r="R8" t="n">
-        <v>7206032</v>
+        <v>7205771</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113231550</v>
+        <v>113231531</v>
       </c>
       <c r="B9" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1493,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546818</v>
+        <v>546605</v>
       </c>
       <c r="R9" t="n">
-        <v>7205855</v>
+        <v>7206002</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113231554</v>
+        <v>113231526</v>
       </c>
       <c r="B10" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1605,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546814</v>
+        <v>546544</v>
       </c>
       <c r="R10" t="n">
-        <v>7205823</v>
+        <v>7206041</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113231553</v>
+        <v>113231561</v>
       </c>
       <c r="B11" t="n">
-        <v>56766</v>
+        <v>74339</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,39 +1717,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546814</v>
+        <v>546831</v>
       </c>
       <c r="R11" t="n">
-        <v>7205823</v>
+        <v>7205718</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113231551</v>
+        <v>113231557</v>
       </c>
       <c r="B12" t="n">
-        <v>56766</v>
+        <v>78158</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,39 +1829,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546819</v>
+        <v>546821</v>
       </c>
       <c r="R12" t="n">
-        <v>7205844</v>
+        <v>7205743</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1898,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113231556</v>
+        <v>113231560</v>
       </c>
       <c r="B13" t="n">
-        <v>56873</v>
+        <v>56914</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1937,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1961,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546836</v>
+        <v>546825</v>
       </c>
       <c r="R13" t="n">
-        <v>7205771</v>
+        <v>7205775</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1996,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113231536</v>
+        <v>113231544</v>
       </c>
       <c r="B14" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546624</v>
+        <v>546727</v>
       </c>
       <c r="R14" t="n">
-        <v>7205956</v>
+        <v>7205919</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2108,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113231521</v>
+        <v>113231563</v>
       </c>
       <c r="B15" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546488</v>
+        <v>546831</v>
       </c>
       <c r="R15" t="n">
-        <v>7205982</v>
+        <v>7205718</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2220,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113231552</v>
+        <v>113231543</v>
       </c>
       <c r="B16" t="n">
-        <v>78155</v>
+        <v>56769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,34 +2281,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546819</v>
+        <v>546727</v>
       </c>
       <c r="R16" t="n">
-        <v>7205843</v>
+        <v>7205919</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2332,7 +2345,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2355,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113231541</v>
+        <v>113231540</v>
       </c>
       <c r="B17" t="n">
-        <v>78155</v>
+        <v>90101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2385,21 +2398,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2484,7 +2497,7 @@
         <v>113231545</v>
       </c>
       <c r="B18" t="n">
-        <v>79219</v>
+        <v>79223</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2593,10 +2606,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113231558</v>
+        <v>113231512</v>
       </c>
       <c r="B19" t="n">
-        <v>79219</v>
+        <v>79223</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546816</v>
+        <v>546610</v>
       </c>
       <c r="R19" t="n">
-        <v>7205730</v>
+        <v>7205953</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2668,7 +2681,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,7 +2691,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,10 +2718,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113231518</v>
+        <v>113231548</v>
       </c>
       <c r="B20" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2745,10 +2758,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546433</v>
+        <v>546793</v>
       </c>
       <c r="R20" t="n">
-        <v>7205978</v>
+        <v>7205849</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,7 +2793,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2803,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113231561</v>
+        <v>113231529</v>
       </c>
       <c r="B21" t="n">
-        <v>74336</v>
+        <v>79223</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,21 +2846,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2857,10 +2870,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546831</v>
+        <v>546577</v>
       </c>
       <c r="R21" t="n">
-        <v>7205718</v>
+        <v>7206034</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2905,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2915,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113231535</v>
+        <v>113231532</v>
       </c>
       <c r="B22" t="n">
-        <v>90639</v>
+        <v>79256</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,25 +2954,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2982,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546623</v>
+        <v>546604</v>
       </c>
       <c r="R22" t="n">
-        <v>7205959</v>
+        <v>7206002</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3004,7 +3017,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +3027,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113231528</v>
+        <v>113231536</v>
       </c>
       <c r="B23" t="n">
-        <v>90761</v>
+        <v>78158</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,25 +3066,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3081,10 +3094,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546576</v>
+        <v>546624</v>
       </c>
       <c r="R23" t="n">
-        <v>7206034</v>
+        <v>7205956</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3116,7 +3129,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3126,7 +3139,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,10 +3166,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113231562</v>
+        <v>113231514</v>
       </c>
       <c r="B24" t="n">
-        <v>90097</v>
+        <v>78158</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,21 +3182,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +3206,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546830</v>
+        <v>546602</v>
       </c>
       <c r="R24" t="n">
-        <v>7205715</v>
+        <v>7205952</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3228,7 +3241,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3251,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,10 +3278,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113231549</v>
+        <v>113231785</v>
       </c>
       <c r="B25" t="n">
-        <v>56766</v>
+        <v>57366</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3277,20 +3290,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3298,10 +3311,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3310,10 +3322,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546817</v>
+        <v>546816</v>
       </c>
       <c r="R25" t="n">
-        <v>7205855</v>
+        <v>7205730</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,7 +3357,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3367,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,10 +3394,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113231560</v>
+        <v>113231530</v>
       </c>
       <c r="B26" t="n">
-        <v>56911</v>
+        <v>78158</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3398,38 +3410,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546825</v>
+        <v>546576</v>
       </c>
       <c r="R26" t="n">
-        <v>7205775</v>
+        <v>7206032</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3461,7 +3469,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3471,7 +3479,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3498,10 +3506,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113231547</v>
+        <v>113231521</v>
       </c>
       <c r="B27" t="n">
-        <v>74332</v>
+        <v>78158</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3514,21 +3522,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3538,10 +3546,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546793</v>
+        <v>546488</v>
       </c>
       <c r="R27" t="n">
-        <v>7205849</v>
+        <v>7205982</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3573,7 +3581,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3583,7 +3591,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3610,10 +3618,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113231526</v>
+        <v>113231558</v>
       </c>
       <c r="B28" t="n">
-        <v>79219</v>
+        <v>79223</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3650,10 +3658,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546544</v>
+        <v>546816</v>
       </c>
       <c r="R28" t="n">
-        <v>7206041</v>
+        <v>7205730</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3685,7 +3693,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3695,7 +3703,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3722,10 +3730,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113231531</v>
+        <v>113231554</v>
       </c>
       <c r="B29" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3738,21 +3746,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3762,10 +3770,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546605</v>
+        <v>546814</v>
       </c>
       <c r="R29" t="n">
-        <v>7206002</v>
+        <v>7205823</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3797,7 +3805,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3807,7 +3815,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3834,10 +3842,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113231523</v>
+        <v>113231546</v>
       </c>
       <c r="B30" t="n">
-        <v>56911</v>
+        <v>78158</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3850,43 +3858,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546496</v>
+        <v>546772</v>
       </c>
       <c r="R30" t="n">
-        <v>7205950</v>
+        <v>7205856</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3918,7 +3917,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3928,7 +3927,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3955,10 +3954,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113231542</v>
+        <v>113231525</v>
       </c>
       <c r="B31" t="n">
-        <v>79219</v>
+        <v>79249</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3967,25 +3966,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3995,10 +3994,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546717</v>
+        <v>546543</v>
       </c>
       <c r="R31" t="n">
-        <v>7205909</v>
+        <v>7206040</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4030,7 +4029,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4040,7 +4039,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4066,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113231517</v>
+        <v>113231549</v>
       </c>
       <c r="B32" t="n">
-        <v>74336</v>
+        <v>56769</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4083,34 +4082,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546435</v>
+        <v>546817</v>
       </c>
       <c r="R32" t="n">
-        <v>7205979</v>
+        <v>7205855</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4142,7 +4146,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,7 +4156,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4179,10 +4183,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113231525</v>
+        <v>113231518</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>78158</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4191,25 +4195,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4219,10 +4223,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546543</v>
+        <v>546433</v>
       </c>
       <c r="R33" t="n">
-        <v>7206040</v>
+        <v>7205978</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4254,7 +4258,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,7 +4268,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4291,10 +4295,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113231544</v>
+        <v>113231533</v>
       </c>
       <c r="B34" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4331,10 +4335,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546727</v>
+        <v>546607</v>
       </c>
       <c r="R34" t="n">
-        <v>7205919</v>
+        <v>7206002</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4366,7 +4370,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4376,7 +4380,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4403,10 +4407,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113231533</v>
+        <v>113231516</v>
       </c>
       <c r="B35" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4443,10 +4447,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546607</v>
+        <v>546573</v>
       </c>
       <c r="R35" t="n">
-        <v>7206002</v>
+        <v>7205984</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4478,7 +4482,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4492,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,10 +4519,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113231516</v>
+        <v>113231513</v>
       </c>
       <c r="B36" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4531,21 +4535,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4555,10 +4559,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546573</v>
+        <v>546603</v>
       </c>
       <c r="R36" t="n">
-        <v>7205984</v>
+        <v>7205952</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4590,7 +4594,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4604,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4627,10 +4631,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113231540</v>
+        <v>113231562</v>
       </c>
       <c r="B37" t="n">
-        <v>90097</v>
+        <v>90101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4667,10 +4671,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546672</v>
+        <v>546830</v>
       </c>
       <c r="R37" t="n">
-        <v>7205887</v>
+        <v>7205715</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4702,7 +4706,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4712,7 +4716,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4739,10 +4743,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113231555</v>
+        <v>113231547</v>
       </c>
       <c r="B38" t="n">
-        <v>79219</v>
+        <v>74335</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4755,21 +4759,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4779,10 +4783,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546821</v>
+        <v>546793</v>
       </c>
       <c r="R38" t="n">
-        <v>7205745</v>
+        <v>7205849</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4814,7 +4818,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4824,7 +4828,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4851,10 +4855,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113231534</v>
+        <v>113231551</v>
       </c>
       <c r="B39" t="n">
-        <v>79219</v>
+        <v>56769</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4867,34 +4871,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546624</v>
+        <v>546819</v>
       </c>
       <c r="R39" t="n">
-        <v>7205957</v>
+        <v>7205844</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4926,7 +4935,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4936,7 +4945,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4963,10 +4972,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113231513</v>
+        <v>113231524</v>
       </c>
       <c r="B40" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4979,21 +4988,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5003,10 +5012,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546603</v>
+        <v>546496</v>
       </c>
       <c r="R40" t="n">
-        <v>7205952</v>
+        <v>7205951</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5038,7 +5047,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5048,7 +5057,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5075,10 +5084,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113231529</v>
+        <v>113231538</v>
       </c>
       <c r="B41" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5091,21 +5100,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5115,10 +5124,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546577</v>
+        <v>546640</v>
       </c>
       <c r="R41" t="n">
-        <v>7206034</v>
+        <v>7205922</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5150,7 +5159,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5160,7 +5169,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5187,10 +5196,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113231785</v>
+        <v>113231541</v>
       </c>
       <c r="B42" t="n">
-        <v>57363</v>
+        <v>78158</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5199,42 +5208,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546816</v>
+        <v>546672</v>
       </c>
       <c r="R42" t="n">
-        <v>7205730</v>
+        <v>7205887</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5266,7 +5271,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5276,7 +5281,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5303,10 +5308,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113231537</v>
+        <v>113231542</v>
       </c>
       <c r="B43" t="n">
-        <v>79218</v>
+        <v>79223</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5319,21 +5324,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5343,10 +5348,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546642</v>
+        <v>546717</v>
       </c>
       <c r="R43" t="n">
-        <v>7205923</v>
+        <v>7205909</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5378,7 +5383,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5388,7 +5393,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5415,10 +5420,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113231559</v>
+        <v>113231515</v>
       </c>
       <c r="B44" t="n">
-        <v>79252</v>
+        <v>79223</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5427,25 +5432,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5455,10 +5460,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546819</v>
+        <v>546574</v>
       </c>
       <c r="R44" t="n">
-        <v>7205732</v>
+        <v>7205984</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5490,7 +5495,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5500,7 +5505,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5527,10 +5532,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113231546</v>
+        <v>113231519</v>
       </c>
       <c r="B45" t="n">
-        <v>78155</v>
+        <v>90083</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5543,21 +5548,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5567,10 +5572,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546772</v>
+        <v>546487</v>
       </c>
       <c r="R45" t="n">
-        <v>7205856</v>
+        <v>7205984</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5602,7 +5607,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5612,7 +5617,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5639,10 +5644,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113231543</v>
+        <v>113231550</v>
       </c>
       <c r="B46" t="n">
-        <v>56766</v>
+        <v>78158</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5655,39 +5660,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546727</v>
+        <v>546818</v>
       </c>
       <c r="R46" t="n">
-        <v>7205919</v>
+        <v>7205855</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5756,10 +5756,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113231519</v>
+        <v>113231555</v>
       </c>
       <c r="B47" t="n">
-        <v>90079</v>
+        <v>79223</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5772,21 +5772,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546487</v>
+        <v>546821</v>
       </c>
       <c r="R47" t="n">
-        <v>7205984</v>
+        <v>7205745</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5868,10 +5868,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113231539</v>
+        <v>113231535</v>
       </c>
       <c r="B48" t="n">
-        <v>90421</v>
+        <v>90643</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2063</v>
+        <v>760</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546673</v>
+        <v>546623</v>
       </c>
       <c r="R48" t="n">
-        <v>7205890</v>
+        <v>7205959</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5980,10 +5980,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113231524</v>
+        <v>113231552</v>
       </c>
       <c r="B49" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546496</v>
+        <v>546819</v>
       </c>
       <c r="R49" t="n">
-        <v>7205951</v>
+        <v>7205843</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6092,10 +6092,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113231557</v>
+        <v>113231534</v>
       </c>
       <c r="B50" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6108,21 +6108,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546821</v>
+        <v>546624</v>
       </c>
       <c r="R50" t="n">
-        <v>7205743</v>
+        <v>7205957</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6204,10 +6204,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113231514</v>
+        <v>113231539</v>
       </c>
       <c r="B51" t="n">
-        <v>78155</v>
+        <v>90425</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6216,25 +6216,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546602</v>
+        <v>546673</v>
       </c>
       <c r="R51" t="n">
-        <v>7205952</v>
+        <v>7205890</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6316,10 +6316,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113231538</v>
+        <v>113231559</v>
       </c>
       <c r="B52" t="n">
-        <v>78155</v>
+        <v>79256</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6328,25 +6328,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546640</v>
+        <v>546819</v>
       </c>
       <c r="R52" t="n">
-        <v>7205922</v>
+        <v>7205732</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -2718,10 +2718,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113231548</v>
+        <v>113231529</v>
       </c>
       <c r="B20" t="n">
-        <v>78158</v>
+        <v>79223</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2734,21 +2734,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546793</v>
+        <v>546577</v>
       </c>
       <c r="R20" t="n">
-        <v>7205849</v>
+        <v>7206034</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113231529</v>
+        <v>113231548</v>
       </c>
       <c r="B21" t="n">
-        <v>79223</v>
+        <v>78158</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546577</v>
+        <v>546793</v>
       </c>
       <c r="R21" t="n">
-        <v>7206034</v>
+        <v>7205849</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113231528</v>
+        <v>113231544</v>
       </c>
       <c r="B2" t="n">
-        <v>90765</v>
+        <v>78164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546576</v>
+        <v>546727</v>
       </c>
       <c r="R2" t="n">
-        <v>7206034</v>
+        <v>7205919</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113231537</v>
+        <v>113231559</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>79262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546642</v>
+        <v>546819</v>
       </c>
       <c r="R3" t="n">
-        <v>7205923</v>
+        <v>7205732</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113231523</v>
+        <v>113231548</v>
       </c>
       <c r="B4" t="n">
-        <v>56914</v>
+        <v>78164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,43 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546496</v>
+        <v>546793</v>
       </c>
       <c r="R4" t="n">
-        <v>7205950</v>
+        <v>7205849</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113231517</v>
+        <v>113231542</v>
       </c>
       <c r="B5" t="n">
-        <v>74339</v>
+        <v>79229</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546435</v>
+        <v>546717</v>
       </c>
       <c r="R5" t="n">
-        <v>7205979</v>
+        <v>7205909</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113231553</v>
+        <v>113231529</v>
       </c>
       <c r="B6" t="n">
-        <v>56769</v>
+        <v>79229</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,39 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546814</v>
+        <v>546577</v>
       </c>
       <c r="R6" t="n">
-        <v>7205823</v>
+        <v>7206034</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113231527</v>
+        <v>113231526</v>
       </c>
       <c r="B7" t="n">
-        <v>79222</v>
+        <v>79229</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1289,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546542</v>
+        <v>546544</v>
       </c>
       <c r="R7" t="n">
-        <v>7206042</v>
+        <v>7206041</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1361,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113231556</v>
+        <v>113231553</v>
       </c>
       <c r="B8" t="n">
-        <v>56876</v>
+        <v>56773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,20 +1359,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1394,9 +1380,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1405,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546836</v>
+        <v>546814</v>
       </c>
       <c r="R8" t="n">
-        <v>7205771</v>
+        <v>7205823</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113231531</v>
+        <v>113231563</v>
       </c>
       <c r="B9" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546605</v>
+        <v>546831</v>
       </c>
       <c r="R9" t="n">
-        <v>7206002</v>
+        <v>7205718</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1552,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113231526</v>
+        <v>113231514</v>
       </c>
       <c r="B10" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1629,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546544</v>
+        <v>546602</v>
       </c>
       <c r="R10" t="n">
-        <v>7206041</v>
+        <v>7205952</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1664,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113231561</v>
+        <v>113231562</v>
       </c>
       <c r="B11" t="n">
-        <v>74339</v>
+        <v>90107</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546831</v>
+        <v>546830</v>
       </c>
       <c r="R11" t="n">
-        <v>7205718</v>
+        <v>7205715</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1813,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113231557</v>
+        <v>113231534</v>
       </c>
       <c r="B12" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,21 +1816,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1853,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546821</v>
+        <v>546624</v>
       </c>
       <c r="R12" t="n">
-        <v>7205743</v>
+        <v>7205957</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1888,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113231560</v>
+        <v>113231547</v>
       </c>
       <c r="B13" t="n">
-        <v>56914</v>
+        <v>74341</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,38 +1928,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546825</v>
+        <v>546793</v>
       </c>
       <c r="R13" t="n">
-        <v>7205775</v>
+        <v>7205849</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2004,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113231544</v>
+        <v>113231536</v>
       </c>
       <c r="B14" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546727</v>
+        <v>546624</v>
       </c>
       <c r="R14" t="n">
-        <v>7205919</v>
+        <v>7205956</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2116,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113231563</v>
+        <v>113231535</v>
       </c>
       <c r="B15" t="n">
-        <v>78158</v>
+        <v>90649</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,25 +2148,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2193,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546831</v>
+        <v>546623</v>
       </c>
       <c r="R15" t="n">
-        <v>7205718</v>
+        <v>7205959</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2228,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113231543</v>
+        <v>113231540</v>
       </c>
       <c r="B16" t="n">
-        <v>56769</v>
+        <v>90107</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,39 +2264,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546727</v>
+        <v>546672</v>
       </c>
       <c r="R16" t="n">
-        <v>7205919</v>
+        <v>7205887</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2345,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2355,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113231540</v>
+        <v>113231538</v>
       </c>
       <c r="B17" t="n">
-        <v>90101</v>
+        <v>78164</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,21 +2376,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2422,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546672</v>
+        <v>546640</v>
       </c>
       <c r="R17" t="n">
-        <v>7205887</v>
+        <v>7205922</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2457,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2467,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113231545</v>
+        <v>113231528</v>
       </c>
       <c r="B18" t="n">
-        <v>79223</v>
+        <v>90771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2506,25 +2484,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2534,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546772</v>
+        <v>546576</v>
       </c>
       <c r="R18" t="n">
-        <v>7205856</v>
+        <v>7206034</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2569,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2579,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2606,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113231512</v>
+        <v>113231550</v>
       </c>
       <c r="B19" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2622,21 +2600,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2646,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546610</v>
+        <v>546818</v>
       </c>
       <c r="R19" t="n">
-        <v>7205953</v>
+        <v>7205855</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2681,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113231529</v>
+        <v>113231523</v>
       </c>
       <c r="B20" t="n">
-        <v>79223</v>
+        <v>56918</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2734,34 +2712,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546577</v>
+        <v>546496</v>
       </c>
       <c r="R20" t="n">
-        <v>7206034</v>
+        <v>7205950</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2793,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2803,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2830,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113231548</v>
+        <v>113231785</v>
       </c>
       <c r="B21" t="n">
-        <v>78158</v>
+        <v>57370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2842,38 +2829,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546793</v>
+        <v>546816</v>
       </c>
       <c r="R21" t="n">
-        <v>7205849</v>
+        <v>7205730</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2905,7 +2896,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,7 +2906,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,10 +2933,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113231532</v>
+        <v>113231525</v>
       </c>
       <c r="B22" t="n">
-        <v>79256</v>
+        <v>79255</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2958,21 +2949,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2982,10 +2973,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546604</v>
+        <v>546543</v>
       </c>
       <c r="R22" t="n">
-        <v>7206002</v>
+        <v>7206040</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3017,7 +3008,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3027,7 +3018,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3054,10 +3045,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113231536</v>
+        <v>113231557</v>
       </c>
       <c r="B23" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3094,10 +3085,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546624</v>
+        <v>546821</v>
       </c>
       <c r="R23" t="n">
-        <v>7205956</v>
+        <v>7205743</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3129,7 +3120,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3139,7 +3130,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3166,10 +3157,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113231514</v>
+        <v>113231519</v>
       </c>
       <c r="B24" t="n">
-        <v>78158</v>
+        <v>90089</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3182,21 +3173,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3206,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546602</v>
+        <v>546487</v>
       </c>
       <c r="R24" t="n">
-        <v>7205952</v>
+        <v>7205984</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3241,7 +3232,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3251,7 +3242,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3278,10 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113231785</v>
+        <v>113231537</v>
       </c>
       <c r="B25" t="n">
-        <v>57366</v>
+        <v>79228</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3290,42 +3281,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102125</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546816</v>
+        <v>546642</v>
       </c>
       <c r="R25" t="n">
-        <v>7205730</v>
+        <v>7205923</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3357,7 +3344,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3367,7 +3354,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3394,10 +3381,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113231530</v>
+        <v>113231556</v>
       </c>
       <c r="B26" t="n">
-        <v>78158</v>
+        <v>56880</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3406,38 +3393,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546576</v>
+        <v>546836</v>
       </c>
       <c r="R26" t="n">
-        <v>7206032</v>
+        <v>7205771</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3469,7 +3460,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3479,7 +3470,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3506,10 +3497,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113231521</v>
+        <v>113231543</v>
       </c>
       <c r="B27" t="n">
-        <v>78158</v>
+        <v>56773</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3522,34 +3513,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546488</v>
+        <v>546727</v>
       </c>
       <c r="R27" t="n">
-        <v>7205982</v>
+        <v>7205919</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3581,7 +3577,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3591,7 +3587,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3618,10 +3614,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113231558</v>
+        <v>113231517</v>
       </c>
       <c r="B28" t="n">
-        <v>79223</v>
+        <v>74345</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3634,21 +3630,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3658,10 +3654,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546816</v>
+        <v>546435</v>
       </c>
       <c r="R28" t="n">
-        <v>7205730</v>
+        <v>7205979</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3693,7 +3689,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3703,7 +3699,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3730,10 +3726,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113231554</v>
+        <v>113231512</v>
       </c>
       <c r="B29" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3746,21 +3742,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3770,10 +3766,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546814</v>
+        <v>546610</v>
       </c>
       <c r="R29" t="n">
-        <v>7205823</v>
+        <v>7205953</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3805,7 +3801,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3815,7 +3811,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3842,10 +3838,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113231546</v>
+        <v>113231545</v>
       </c>
       <c r="B30" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,21 +3854,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3954,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113231525</v>
+        <v>113231561</v>
       </c>
       <c r="B31" t="n">
-        <v>79249</v>
+        <v>74345</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,25 +3962,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3994,10 +3990,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546543</v>
+        <v>546831</v>
       </c>
       <c r="R31" t="n">
-        <v>7206040</v>
+        <v>7205718</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4029,7 +4025,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4039,7 +4035,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113231549</v>
+        <v>113231541</v>
       </c>
       <c r="B32" t="n">
-        <v>56769</v>
+        <v>78164</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4082,39 +4078,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546817</v>
+        <v>546672</v>
       </c>
       <c r="R32" t="n">
-        <v>7205855</v>
+        <v>7205887</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4146,7 +4137,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4156,7 +4147,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4183,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113231518</v>
+        <v>113231558</v>
       </c>
       <c r="B33" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4199,21 +4190,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4223,10 +4214,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546433</v>
+        <v>546816</v>
       </c>
       <c r="R33" t="n">
-        <v>7205978</v>
+        <v>7205730</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4258,7 +4249,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4268,7 +4259,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4295,10 +4286,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113231533</v>
+        <v>113231554</v>
       </c>
       <c r="B34" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4335,10 +4326,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546607</v>
+        <v>546814</v>
       </c>
       <c r="R34" t="n">
-        <v>7206002</v>
+        <v>7205823</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4370,7 +4361,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4380,7 +4371,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4407,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113231516</v>
+        <v>113231527</v>
       </c>
       <c r="B35" t="n">
-        <v>78158</v>
+        <v>79228</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4423,21 +4414,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4447,10 +4438,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546573</v>
+        <v>546542</v>
       </c>
       <c r="R35" t="n">
-        <v>7205984</v>
+        <v>7206042</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4482,7 +4473,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4492,7 +4483,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4519,10 +4510,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113231513</v>
+        <v>113231530</v>
       </c>
       <c r="B36" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4535,21 +4526,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4559,10 +4550,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546603</v>
+        <v>546576</v>
       </c>
       <c r="R36" t="n">
-        <v>7205952</v>
+        <v>7206032</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4594,7 +4585,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4604,7 +4595,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4631,10 +4622,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113231562</v>
+        <v>113231539</v>
       </c>
       <c r="B37" t="n">
-        <v>90101</v>
+        <v>90431</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4643,25 +4634,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4671,10 +4662,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546830</v>
+        <v>546673</v>
       </c>
       <c r="R37" t="n">
-        <v>7205715</v>
+        <v>7205890</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4706,7 +4697,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4716,7 +4707,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4743,10 +4734,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113231547</v>
+        <v>113231549</v>
       </c>
       <c r="B38" t="n">
-        <v>74335</v>
+        <v>56773</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4759,34 +4750,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546793</v>
+        <v>546817</v>
       </c>
       <c r="R38" t="n">
-        <v>7205849</v>
+        <v>7205855</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4818,7 +4814,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4828,7 +4824,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4855,10 +4851,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113231551</v>
+        <v>113231516</v>
       </c>
       <c r="B39" t="n">
-        <v>56769</v>
+        <v>78164</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4871,39 +4867,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546819</v>
+        <v>546573</v>
       </c>
       <c r="R39" t="n">
-        <v>7205844</v>
+        <v>7205984</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4935,7 +4926,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4945,7 +4936,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4972,10 +4963,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113231524</v>
+        <v>113231552</v>
       </c>
       <c r="B40" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5012,10 +5003,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546496</v>
+        <v>546819</v>
       </c>
       <c r="R40" t="n">
-        <v>7205951</v>
+        <v>7205843</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5047,7 +5038,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5057,7 +5048,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5084,10 +5075,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113231538</v>
+        <v>113231560</v>
       </c>
       <c r="B41" t="n">
-        <v>78158</v>
+        <v>56918</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5100,34 +5091,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546640</v>
+        <v>546825</v>
       </c>
       <c r="R41" t="n">
-        <v>7205922</v>
+        <v>7205775</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5159,7 +5154,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5169,7 +5164,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5196,10 +5191,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113231541</v>
+        <v>113231555</v>
       </c>
       <c r="B42" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5212,21 +5207,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5236,10 +5231,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546672</v>
+        <v>546821</v>
       </c>
       <c r="R42" t="n">
-        <v>7205887</v>
+        <v>7205745</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5271,7 +5266,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5281,7 +5276,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5308,10 +5303,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113231542</v>
+        <v>113231513</v>
       </c>
       <c r="B43" t="n">
-        <v>79223</v>
+        <v>79229</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5348,10 +5343,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546717</v>
+        <v>546603</v>
       </c>
       <c r="R43" t="n">
-        <v>7205909</v>
+        <v>7205952</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5383,7 +5378,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5393,7 +5388,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5420,10 +5415,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113231515</v>
+        <v>113231532</v>
       </c>
       <c r="B44" t="n">
-        <v>79223</v>
+        <v>79262</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5432,25 +5427,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5460,10 +5455,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546574</v>
+        <v>546604</v>
       </c>
       <c r="R44" t="n">
-        <v>7205984</v>
+        <v>7206002</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5495,7 +5490,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5505,7 +5500,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5532,10 +5527,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113231519</v>
+        <v>113231518</v>
       </c>
       <c r="B45" t="n">
-        <v>90083</v>
+        <v>78164</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5548,21 +5543,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5572,10 +5567,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546487</v>
+        <v>546433</v>
       </c>
       <c r="R45" t="n">
-        <v>7205984</v>
+        <v>7205978</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5607,7 +5602,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5617,7 +5612,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5644,10 +5639,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113231550</v>
+        <v>113231531</v>
       </c>
       <c r="B46" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5660,21 +5655,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5684,10 +5679,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546818</v>
+        <v>546605</v>
       </c>
       <c r="R46" t="n">
-        <v>7205855</v>
+        <v>7206002</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5719,7 +5714,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5729,7 +5724,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5756,10 +5751,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113231555</v>
+        <v>113231533</v>
       </c>
       <c r="B47" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5772,21 +5767,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5796,10 +5791,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546821</v>
+        <v>546607</v>
       </c>
       <c r="R47" t="n">
-        <v>7205745</v>
+        <v>7206002</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5831,7 +5826,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5841,7 +5836,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5868,10 +5863,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113231535</v>
+        <v>113231546</v>
       </c>
       <c r="B48" t="n">
-        <v>90643</v>
+        <v>78164</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5880,25 +5875,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5908,10 +5903,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546623</v>
+        <v>546772</v>
       </c>
       <c r="R48" t="n">
-        <v>7205959</v>
+        <v>7205856</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5943,7 +5938,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5953,7 +5948,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5980,10 +5975,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113231552</v>
+        <v>113231521</v>
       </c>
       <c r="B49" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6020,10 +6015,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546819</v>
+        <v>546488</v>
       </c>
       <c r="R49" t="n">
-        <v>7205843</v>
+        <v>7205982</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6055,7 +6050,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6065,7 +6060,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6092,10 +6087,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113231534</v>
+        <v>113231551</v>
       </c>
       <c r="B50" t="n">
-        <v>79223</v>
+        <v>56773</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6108,34 +6103,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546624</v>
+        <v>546819</v>
       </c>
       <c r="R50" t="n">
-        <v>7205957</v>
+        <v>7205844</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6204,10 +6204,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113231539</v>
+        <v>113231515</v>
       </c>
       <c r="B51" t="n">
-        <v>90425</v>
+        <v>79229</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6216,25 +6216,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546673</v>
+        <v>546574</v>
       </c>
       <c r="R51" t="n">
-        <v>7205890</v>
+        <v>7205984</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6316,10 +6316,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113231559</v>
+        <v>113231524</v>
       </c>
       <c r="B52" t="n">
-        <v>79256</v>
+        <v>78164</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6328,25 +6328,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546819</v>
+        <v>546496</v>
       </c>
       <c r="R52" t="n">
-        <v>7205732</v>
+        <v>7205951</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113231559</v>
+        <v>113231548</v>
       </c>
       <c r="B3" t="n">
-        <v>79262</v>
+        <v>78164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546819</v>
+        <v>546793</v>
       </c>
       <c r="R3" t="n">
-        <v>7205732</v>
+        <v>7205849</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113231548</v>
+        <v>113231559</v>
       </c>
       <c r="B4" t="n">
-        <v>78164</v>
+        <v>79262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546793</v>
+        <v>546819</v>
       </c>
       <c r="R4" t="n">
-        <v>7205849</v>
+        <v>7205732</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -4963,10 +4963,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113231552</v>
+        <v>113231560</v>
       </c>
       <c r="B40" t="n">
-        <v>78164</v>
+        <v>56918</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4979,34 +4979,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546819</v>
+        <v>546825</v>
       </c>
       <c r="R40" t="n">
-        <v>7205843</v>
+        <v>7205775</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5038,7 +5042,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5048,7 +5052,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5075,10 +5079,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113231560</v>
+        <v>113231552</v>
       </c>
       <c r="B41" t="n">
-        <v>56918</v>
+        <v>78164</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5091,38 +5095,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546825</v>
+        <v>546819</v>
       </c>
       <c r="R41" t="n">
-        <v>7205775</v>
+        <v>7205843</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6204,10 +6204,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113231515</v>
+        <v>113231524</v>
       </c>
       <c r="B51" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6220,21 +6220,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546574</v>
+        <v>546496</v>
       </c>
       <c r="R51" t="n">
-        <v>7205984</v>
+        <v>7205951</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6316,10 +6316,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113231524</v>
+        <v>113231515</v>
       </c>
       <c r="B52" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6332,21 +6332,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546496</v>
+        <v>546574</v>
       </c>
       <c r="R52" t="n">
-        <v>7205951</v>
+        <v>7205984</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113231544</v>
+        <v>113231536</v>
       </c>
       <c r="B2" t="n">
         <v>78164</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546727</v>
+        <v>546624</v>
       </c>
       <c r="R2" t="n">
-        <v>7205919</v>
+        <v>7205956</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113231548</v>
+        <v>113231525</v>
       </c>
       <c r="B3" t="n">
-        <v>78164</v>
+        <v>79255</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546793</v>
+        <v>546543</v>
       </c>
       <c r="R3" t="n">
-        <v>7205849</v>
+        <v>7206040</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113231559</v>
+        <v>113231545</v>
       </c>
       <c r="B4" t="n">
-        <v>79262</v>
+        <v>79229</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546819</v>
+        <v>546772</v>
       </c>
       <c r="R4" t="n">
-        <v>7205732</v>
+        <v>7205856</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113231542</v>
+        <v>113231530</v>
       </c>
       <c r="B5" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546717</v>
+        <v>546576</v>
       </c>
       <c r="R5" t="n">
-        <v>7205909</v>
+        <v>7206032</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113231529</v>
+        <v>113231524</v>
       </c>
       <c r="B6" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546577</v>
+        <v>546496</v>
       </c>
       <c r="R6" t="n">
-        <v>7206034</v>
+        <v>7205951</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113231526</v>
+        <v>113231563</v>
       </c>
       <c r="B7" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546544</v>
+        <v>546831</v>
       </c>
       <c r="R7" t="n">
-        <v>7206041</v>
+        <v>7205718</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113231563</v>
+        <v>113231540</v>
       </c>
       <c r="B9" t="n">
-        <v>78164</v>
+        <v>90107</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546831</v>
+        <v>546672</v>
       </c>
       <c r="R9" t="n">
-        <v>7205718</v>
+        <v>7205887</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113231514</v>
+        <v>113231561</v>
       </c>
       <c r="B10" t="n">
-        <v>78164</v>
+        <v>74345</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546602</v>
+        <v>546831</v>
       </c>
       <c r="R10" t="n">
-        <v>7205952</v>
+        <v>7205718</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113231562</v>
+        <v>113231513</v>
       </c>
       <c r="B11" t="n">
-        <v>90107</v>
+        <v>79229</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546830</v>
+        <v>546603</v>
       </c>
       <c r="R11" t="n">
-        <v>7205715</v>
+        <v>7205952</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113231534</v>
+        <v>113231516</v>
       </c>
       <c r="B12" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546624</v>
+        <v>546573</v>
       </c>
       <c r="R12" t="n">
-        <v>7205957</v>
+        <v>7205984</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113231547</v>
+        <v>113231527</v>
       </c>
       <c r="B13" t="n">
-        <v>74341</v>
+        <v>79228</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>310</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546793</v>
+        <v>546542</v>
       </c>
       <c r="R13" t="n">
-        <v>7205849</v>
+        <v>7206042</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,7 +2024,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113231536</v>
+        <v>113231557</v>
       </c>
       <c r="B14" t="n">
         <v>78164</v>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546624</v>
+        <v>546821</v>
       </c>
       <c r="R14" t="n">
-        <v>7205956</v>
+        <v>7205743</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113231535</v>
+        <v>113231512</v>
       </c>
       <c r="B15" t="n">
-        <v>90649</v>
+        <v>79229</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,25 +2148,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546623</v>
+        <v>546610</v>
       </c>
       <c r="R15" t="n">
-        <v>7205959</v>
+        <v>7205953</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113231540</v>
+        <v>113231539</v>
       </c>
       <c r="B16" t="n">
-        <v>90107</v>
+        <v>90431</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546672</v>
+        <v>546673</v>
       </c>
       <c r="R16" t="n">
-        <v>7205887</v>
+        <v>7205890</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113231538</v>
+        <v>113231534</v>
       </c>
       <c r="B17" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,21 +2376,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546640</v>
+        <v>546624</v>
       </c>
       <c r="R17" t="n">
-        <v>7205922</v>
+        <v>7205957</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113231528</v>
+        <v>113231538</v>
       </c>
       <c r="B18" t="n">
-        <v>90771</v>
+        <v>78164</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,25 +2484,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546576</v>
+        <v>546640</v>
       </c>
       <c r="R18" t="n">
-        <v>7206034</v>
+        <v>7205922</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113231550</v>
+        <v>113231558</v>
       </c>
       <c r="B19" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,21 +2600,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546818</v>
+        <v>546816</v>
       </c>
       <c r="R19" t="n">
-        <v>7205855</v>
+        <v>7205730</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113231523</v>
+        <v>113231515</v>
       </c>
       <c r="B20" t="n">
-        <v>56918</v>
+        <v>79229</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,43 +2712,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546496</v>
+        <v>546574</v>
       </c>
       <c r="R20" t="n">
-        <v>7205950</v>
+        <v>7205984</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113231785</v>
+        <v>113231532</v>
       </c>
       <c r="B21" t="n">
-        <v>57370</v>
+        <v>79262</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,42 +2820,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102125</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546816</v>
+        <v>546604</v>
       </c>
       <c r="R21" t="n">
-        <v>7205730</v>
+        <v>7206002</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2896,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2906,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2933,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113231525</v>
+        <v>113231550</v>
       </c>
       <c r="B22" t="n">
-        <v>79255</v>
+        <v>78164</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2945,25 +2932,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2973,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546543</v>
+        <v>546818</v>
       </c>
       <c r="R22" t="n">
-        <v>7206040</v>
+        <v>7205855</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3008,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3018,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113231557</v>
+        <v>113231528</v>
       </c>
       <c r="B23" t="n">
-        <v>78164</v>
+        <v>90771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,25 +3044,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3085,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546821</v>
+        <v>546576</v>
       </c>
       <c r="R23" t="n">
-        <v>7205743</v>
+        <v>7206034</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3120,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3130,7 +3117,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3157,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113231519</v>
+        <v>113231560</v>
       </c>
       <c r="B24" t="n">
-        <v>90089</v>
+        <v>56918</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3173,34 +3160,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546487</v>
+        <v>546825</v>
       </c>
       <c r="R24" t="n">
-        <v>7205984</v>
+        <v>7205775</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3232,7 +3223,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3242,7 +3233,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3269,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113231537</v>
+        <v>113231514</v>
       </c>
       <c r="B25" t="n">
-        <v>79228</v>
+        <v>78164</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,21 +3276,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3309,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546642</v>
+        <v>546602</v>
       </c>
       <c r="R25" t="n">
-        <v>7205923</v>
+        <v>7205952</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3344,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3354,7 +3345,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3381,10 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113231556</v>
+        <v>113231552</v>
       </c>
       <c r="B26" t="n">
-        <v>56880</v>
+        <v>78164</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3393,42 +3384,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546836</v>
+        <v>546819</v>
       </c>
       <c r="R26" t="n">
-        <v>7205771</v>
+        <v>7205843</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3460,7 +3447,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3470,7 +3457,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3497,10 +3484,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113231543</v>
+        <v>113231562</v>
       </c>
       <c r="B27" t="n">
-        <v>56773</v>
+        <v>90107</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3513,39 +3500,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546727</v>
+        <v>546830</v>
       </c>
       <c r="R27" t="n">
-        <v>7205919</v>
+        <v>7205715</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3577,7 +3559,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3587,7 +3569,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3614,10 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113231517</v>
+        <v>113231523</v>
       </c>
       <c r="B28" t="n">
-        <v>74345</v>
+        <v>56918</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3630,34 +3612,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546435</v>
+        <v>546496</v>
       </c>
       <c r="R28" t="n">
-        <v>7205979</v>
+        <v>7205950</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3689,7 +3680,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3699,7 +3690,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,7 +3717,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113231512</v>
+        <v>113231555</v>
       </c>
       <c r="B29" t="n">
         <v>79229</v>
@@ -3766,10 +3757,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546610</v>
+        <v>546821</v>
       </c>
       <c r="R29" t="n">
-        <v>7205953</v>
+        <v>7205745</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3801,7 +3792,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3811,7 +3802,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3838,7 +3829,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113231545</v>
+        <v>113231531</v>
       </c>
       <c r="B30" t="n">
         <v>79229</v>
@@ -3878,10 +3869,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546772</v>
+        <v>546605</v>
       </c>
       <c r="R30" t="n">
-        <v>7205856</v>
+        <v>7206002</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3913,7 +3904,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3923,7 +3914,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,10 +3941,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113231561</v>
+        <v>113231533</v>
       </c>
       <c r="B31" t="n">
-        <v>74345</v>
+        <v>78164</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,21 +3957,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3990,10 +3981,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546831</v>
+        <v>546607</v>
       </c>
       <c r="R31" t="n">
-        <v>7205718</v>
+        <v>7206002</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4025,7 +4016,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,7 +4026,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,10 +4053,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113231541</v>
+        <v>113231537</v>
       </c>
       <c r="B32" t="n">
-        <v>78164</v>
+        <v>79228</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4078,21 +4069,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4102,10 +4093,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546672</v>
+        <v>546642</v>
       </c>
       <c r="R32" t="n">
-        <v>7205887</v>
+        <v>7205923</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4137,7 +4128,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,7 +4138,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4174,10 +4165,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113231558</v>
+        <v>113231559</v>
       </c>
       <c r="B33" t="n">
-        <v>79229</v>
+        <v>79262</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4186,25 +4177,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4214,10 +4205,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546816</v>
+        <v>546819</v>
       </c>
       <c r="R33" t="n">
-        <v>7205730</v>
+        <v>7205732</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4286,7 +4277,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113231554</v>
+        <v>113231541</v>
       </c>
       <c r="B34" t="n">
         <v>78164</v>
@@ -4326,10 +4317,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546814</v>
+        <v>546672</v>
       </c>
       <c r="R34" t="n">
-        <v>7205823</v>
+        <v>7205887</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4361,7 +4352,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4371,7 +4362,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4398,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113231527</v>
+        <v>113231518</v>
       </c>
       <c r="B35" t="n">
-        <v>79228</v>
+        <v>78164</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,21 +4405,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4438,10 +4429,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546542</v>
+        <v>546433</v>
       </c>
       <c r="R35" t="n">
-        <v>7206042</v>
+        <v>7205978</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4473,7 +4464,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4483,7 +4474,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4510,7 +4501,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113231530</v>
+        <v>113231521</v>
       </c>
       <c r="B36" t="n">
         <v>78164</v>
@@ -4550,10 +4541,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546576</v>
+        <v>546488</v>
       </c>
       <c r="R36" t="n">
-        <v>7206032</v>
+        <v>7205982</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4585,7 +4576,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4595,7 +4586,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4622,10 +4613,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113231539</v>
+        <v>113231529</v>
       </c>
       <c r="B37" t="n">
-        <v>90431</v>
+        <v>79229</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4634,25 +4625,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4662,10 +4653,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546673</v>
+        <v>546577</v>
       </c>
       <c r="R37" t="n">
-        <v>7205890</v>
+        <v>7206034</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4697,7 +4688,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4707,7 +4698,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4734,10 +4725,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113231549</v>
+        <v>113231542</v>
       </c>
       <c r="B38" t="n">
-        <v>56773</v>
+        <v>79229</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4750,39 +4741,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546817</v>
+        <v>546717</v>
       </c>
       <c r="R38" t="n">
-        <v>7205855</v>
+        <v>7205909</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4814,7 +4800,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4824,7 +4810,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4851,7 +4837,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113231516</v>
+        <v>113231546</v>
       </c>
       <c r="B39" t="n">
         <v>78164</v>
@@ -4891,10 +4877,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546573</v>
+        <v>546772</v>
       </c>
       <c r="R39" t="n">
-        <v>7205984</v>
+        <v>7205856</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4926,7 +4912,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4936,7 +4922,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4963,10 +4949,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113231560</v>
+        <v>113231548</v>
       </c>
       <c r="B40" t="n">
-        <v>56918</v>
+        <v>78164</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4979,38 +4965,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546825</v>
+        <v>546793</v>
       </c>
       <c r="R40" t="n">
-        <v>7205775</v>
+        <v>7205849</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5042,7 +5024,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5052,7 +5034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5079,7 +5061,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113231552</v>
+        <v>113231544</v>
       </c>
       <c r="B41" t="n">
         <v>78164</v>
@@ -5119,10 +5101,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546819</v>
+        <v>546727</v>
       </c>
       <c r="R41" t="n">
-        <v>7205843</v>
+        <v>7205919</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5154,7 +5136,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5164,7 +5146,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5191,10 +5173,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113231555</v>
+        <v>113231554</v>
       </c>
       <c r="B42" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5207,21 +5189,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5231,10 +5213,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546821</v>
+        <v>546814</v>
       </c>
       <c r="R42" t="n">
-        <v>7205745</v>
+        <v>7205823</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5266,7 +5248,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5276,7 +5258,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5303,10 +5285,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113231513</v>
+        <v>113231549</v>
       </c>
       <c r="B43" t="n">
-        <v>79229</v>
+        <v>56773</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5319,34 +5301,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546603</v>
+        <v>546817</v>
       </c>
       <c r="R43" t="n">
-        <v>7205952</v>
+        <v>7205855</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5378,7 +5365,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5388,7 +5375,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5415,10 +5402,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113231532</v>
+        <v>113231556</v>
       </c>
       <c r="B44" t="n">
-        <v>79262</v>
+        <v>56880</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5431,34 +5418,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>103031</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546604</v>
+        <v>546836</v>
       </c>
       <c r="R44" t="n">
-        <v>7206002</v>
+        <v>7205771</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5490,7 +5481,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5500,7 +5491,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5527,10 +5518,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113231518</v>
+        <v>113231517</v>
       </c>
       <c r="B45" t="n">
-        <v>78164</v>
+        <v>74345</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5543,21 +5534,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5567,10 +5558,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546433</v>
+        <v>546435</v>
       </c>
       <c r="R45" t="n">
-        <v>7205978</v>
+        <v>7205979</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5639,10 +5630,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113231531</v>
+        <v>113231535</v>
       </c>
       <c r="B46" t="n">
-        <v>79229</v>
+        <v>90649</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5651,25 +5642,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5679,10 +5670,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546605</v>
+        <v>546623</v>
       </c>
       <c r="R46" t="n">
-        <v>7206002</v>
+        <v>7205959</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5714,7 +5705,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5724,7 +5715,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5751,10 +5742,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113231533</v>
+        <v>113231785</v>
       </c>
       <c r="B47" t="n">
-        <v>78164</v>
+        <v>57370</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5763,38 +5754,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546607</v>
+        <v>546816</v>
       </c>
       <c r="R47" t="n">
-        <v>7206002</v>
+        <v>7205730</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5826,7 +5821,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5836,7 +5831,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5863,10 +5858,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113231546</v>
+        <v>113231519</v>
       </c>
       <c r="B48" t="n">
-        <v>78164</v>
+        <v>90089</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5879,21 +5874,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5903,10 +5898,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546772</v>
+        <v>546487</v>
       </c>
       <c r="R48" t="n">
-        <v>7205856</v>
+        <v>7205984</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5938,7 +5933,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5948,7 +5943,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5975,10 +5970,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113231521</v>
+        <v>113231547</v>
       </c>
       <c r="B49" t="n">
-        <v>78164</v>
+        <v>74341</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5991,21 +5986,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546488</v>
+        <v>546793</v>
       </c>
       <c r="R49" t="n">
-        <v>7205982</v>
+        <v>7205849</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6050,7 +6045,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6060,7 +6055,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6087,10 +6082,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113231551</v>
+        <v>113231526</v>
       </c>
       <c r="B50" t="n">
-        <v>56773</v>
+        <v>79229</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6103,39 +6098,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546819</v>
+        <v>546544</v>
       </c>
       <c r="R50" t="n">
-        <v>7205844</v>
+        <v>7206041</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6167,7 +6157,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6177,7 +6167,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6204,10 +6194,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113231524</v>
+        <v>113231543</v>
       </c>
       <c r="B51" t="n">
-        <v>78164</v>
+        <v>56773</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6220,34 +6210,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546496</v>
+        <v>546727</v>
       </c>
       <c r="R51" t="n">
-        <v>7205951</v>
+        <v>7205919</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6279,7 +6274,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6289,7 +6284,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6316,10 +6311,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113231515</v>
+        <v>113231551</v>
       </c>
       <c r="B52" t="n">
-        <v>79229</v>
+        <v>56773</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6332,34 +6327,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546574</v>
+        <v>546819</v>
       </c>
       <c r="R52" t="n">
-        <v>7205984</v>
+        <v>7205844</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 48244-2023 artfynd.xlsx
+++ b/artfynd/A 48244-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
